--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
   <si>
     <t>生产日期</t>
   </si>
@@ -46,18 +46,6 @@
   </si>
   <si>
     <t>不出原因</t>
-  </si>
-  <si>
-    <t>WG9000360700</t>
-  </si>
-  <si>
-    <t>储气筒</t>
-  </si>
-  <si>
-    <t>王凤玲</t>
-  </si>
-  <si>
-    <t>暂时不出</t>
   </si>
   <si>
     <t>库区编码</t>
@@ -1320,19 +1308,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:2">
       <c r="A22" s="4">
         <v>45232</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="4">
         <v>45233</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="4">
         <v>45234</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -1467,8 +1464,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1488,20 +1485,6 @@
       </c>
       <c r="D1" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1522,37 +1505,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1572,226 +1555,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1815,7 +1798,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -1868,13 +1851,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1885,7 +1868,7 @@
         <v>45240</v>
       </c>
       <c r="C2" s="1">
-        <v>45235</v>
+        <v>45236</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -1865,7 +1865,7 @@
         <v>45229</v>
       </c>
       <c r="B2" s="1">
-        <v>45240</v>
+        <v>45241</v>
       </c>
       <c r="C2" s="1">
         <v>45236</v>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
   <si>
     <t>生产日期</t>
   </si>
@@ -1133,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="11.625" customWidth="1"/>
@@ -1304,49 +1304,75 @@
       <c r="A21" s="4">
         <v>45231</v>
       </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:3">
       <c r="A22" s="4">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="4">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="4">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="C24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="4">
         <v>45235</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="4">
         <v>45236</v>
       </c>
-      <c r="C26" s="5"/>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="4">
         <v>45237</v>
       </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
       <c r="C27" s="5"/>
     </row>
     <row r="28" spans="1:3">
@@ -1359,19 +1385,29 @@
       <c r="A29" s="4">
         <v>45239</v>
       </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
       <c r="C29" s="5"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:2">
       <c r="A30" s="4">
         <v>45240</v>
       </c>
-      <c r="C30" s="5"/>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="4">
         <v>45241</v>
       </c>
-      <c r="C31" s="5"/>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4">
@@ -1453,6 +1489,11 @@
     <row r="47" spans="1:1">
       <c r="A47" s="4">
         <v>45257</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4">
+        <v>45258</v>
       </c>
     </row>
   </sheetData>
@@ -1467,10 +1508,10 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1862,13 +1903,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1">
-        <v>45229</v>
+        <v>45231</v>
       </c>
       <c r="B2" s="1">
-        <v>45241</v>
+        <v>45249</v>
       </c>
       <c r="C2" s="1">
-        <v>45236</v>
+        <v>45246</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
     <sheet name="临时不出库物料表" sheetId="7" r:id="rId2"/>
-    <sheet name="不出库库区表" sheetId="6" r:id="rId3"/>
+    <sheet name="日期配置" sheetId="8" r:id="rId3"/>
     <sheet name="库区表" sheetId="1" r:id="rId4"/>
-    <sheet name="不出库供应商表" sheetId="4" r:id="rId5"/>
-    <sheet name="日期配置" sheetId="8" r:id="rId6"/>
+    <sheet name="不出库库区表" sheetId="6" r:id="rId5"/>
+    <sheet name="不出库供应商表" sheetId="4" r:id="rId6"/>
+    <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
   <si>
     <t>生产日期</t>
   </si>
@@ -36,6 +37,12 @@
     <t>已完成</t>
   </si>
   <si>
+    <t>跨月</t>
+  </si>
+  <si>
+    <t>无排产</t>
+  </si>
+  <si>
     <t>物料编码</t>
   </si>
   <si>
@@ -48,9 +55,138 @@
     <t>不出原因</t>
   </si>
   <si>
+    <t>712W15101-0032</t>
+  </si>
+  <si>
+    <t>SCR国V消音器总成</t>
+  </si>
+  <si>
+    <t>郭宝淇</t>
+  </si>
+  <si>
+    <t>互供物料，进入逆向</t>
+  </si>
+  <si>
+    <t>起始日期</t>
+  </si>
+  <si>
+    <t>截止日期</t>
+  </si>
+  <si>
+    <t>跨分拣截止日期</t>
+  </si>
+  <si>
+    <t>跨分装截止日期</t>
+  </si>
+  <si>
     <t>库区编码</t>
   </si>
   <si>
+    <t>班组</t>
+  </si>
+  <si>
+    <t>312302.C01</t>
+  </si>
+  <si>
+    <t>标准件</t>
+  </si>
+  <si>
+    <t>312302.C02</t>
+  </si>
+  <si>
+    <t>收货</t>
+  </si>
+  <si>
+    <t>312302.C03</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>312302.C04</t>
+  </si>
+  <si>
+    <t>总装</t>
+  </si>
+  <si>
+    <t>312302.C05</t>
+  </si>
+  <si>
+    <t>312302.C06</t>
+  </si>
+  <si>
+    <t>312302.C07</t>
+  </si>
+  <si>
+    <t>312302.C08</t>
+  </si>
+  <si>
+    <t>底盘</t>
+  </si>
+  <si>
+    <t>312302.C09</t>
+  </si>
+  <si>
+    <t>312302.C10</t>
+  </si>
+  <si>
+    <t>312302.C13</t>
+  </si>
+  <si>
+    <t>312302.C21</t>
+  </si>
+  <si>
+    <t>内饰</t>
+  </si>
+  <si>
+    <t>312302.C22</t>
+  </si>
+  <si>
+    <t>312302.C23</t>
+  </si>
+  <si>
+    <t>312302.C24</t>
+  </si>
+  <si>
+    <t>312302.C25</t>
+  </si>
+  <si>
+    <t>312302.C26</t>
+  </si>
+  <si>
+    <t>312302.C27</t>
+  </si>
+  <si>
+    <t>312302.C28</t>
+  </si>
+  <si>
+    <t>312302.C29</t>
+  </si>
+  <si>
+    <t>312302.C30</t>
+  </si>
+  <si>
+    <t>312302.C31</t>
+  </si>
+  <si>
+    <t>312302.C33</t>
+  </si>
+  <si>
+    <t>312302.C35</t>
+  </si>
+  <si>
+    <t>312302.C36</t>
+  </si>
+  <si>
+    <t>312302.C39</t>
+  </si>
+  <si>
+    <t>逆向</t>
+  </si>
+  <si>
+    <t>312302.C41</t>
+  </si>
+  <si>
     <t>312302.C11</t>
   </si>
   <si>
@@ -69,121 +205,28 @@
     <t>312302.C99</t>
   </si>
   <si>
-    <t>班组</t>
-  </si>
-  <si>
-    <t>312302.C01</t>
-  </si>
-  <si>
-    <t>标准件</t>
-  </si>
-  <si>
-    <t>312302.C02</t>
-  </si>
-  <si>
-    <t>收货</t>
-  </si>
-  <si>
-    <t>312302.C03</t>
-  </si>
-  <si>
-    <t>C03</t>
-  </si>
-  <si>
-    <t>312302.C04</t>
-  </si>
-  <si>
-    <t>总装</t>
-  </si>
-  <si>
-    <t>312302.C05</t>
-  </si>
-  <si>
-    <t>312302.C06</t>
-  </si>
-  <si>
-    <t>312302.C07</t>
-  </si>
-  <si>
-    <t>312302.C08</t>
-  </si>
-  <si>
-    <t>底盘</t>
-  </si>
-  <si>
-    <t>312302.C09</t>
-  </si>
-  <si>
-    <t>312302.C10</t>
-  </si>
-  <si>
-    <t>312302.C13</t>
-  </si>
-  <si>
-    <t>312302.C21</t>
-  </si>
-  <si>
-    <t>内饰</t>
-  </si>
-  <si>
-    <t>312302.C22</t>
-  </si>
-  <si>
-    <t>312302.C23</t>
-  </si>
-  <si>
-    <t>312302.C24</t>
-  </si>
-  <si>
-    <t>312302.C25</t>
-  </si>
-  <si>
-    <t>312302.C26</t>
-  </si>
-  <si>
-    <t>312302.C27</t>
-  </si>
-  <si>
-    <t>312302.C28</t>
-  </si>
-  <si>
-    <t>312302.C29</t>
-  </si>
-  <si>
-    <t>312302.C30</t>
-  </si>
-  <si>
-    <t>312302.C31</t>
-  </si>
-  <si>
-    <t>312302.C33</t>
-  </si>
-  <si>
-    <t>312302.C35</t>
-  </si>
-  <si>
-    <t>312302.C36</t>
-  </si>
-  <si>
-    <t>312302.C39</t>
-  </si>
-  <si>
-    <t>逆向</t>
-  </si>
-  <si>
-    <t>312302.C41</t>
-  </si>
-  <si>
     <t>供应商编码</t>
   </si>
   <si>
-    <t>起始日期</t>
-  </si>
-  <si>
-    <t>截止日期</t>
-  </si>
-  <si>
-    <t>跨分拣截止日期</t>
+    <t>工位</t>
+  </si>
+  <si>
+    <t>ZZ01-ZF10</t>
+  </si>
+  <si>
+    <t>ZZ01-ZF08</t>
+  </si>
+  <si>
+    <t>ZZ01-ZD01</t>
+  </si>
+  <si>
+    <t>ZZ02-ZF10</t>
+  </si>
+  <si>
+    <t>ZZ02-ZF08</t>
+  </si>
+  <si>
+    <t>ZZ02-ZD01</t>
   </si>
 </sst>
 </file>
@@ -198,7 +241,21 @@
     <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,143 +728,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -815,10 +872,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="11.625" customWidth="1"/>
@@ -1152,7 +1210,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>45212</v>
       </c>
       <c r="C2" t="s">
@@ -1160,7 +1218,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4">
+      <c r="A3" s="6">
         <v>45213</v>
       </c>
       <c r="C3" t="s">
@@ -1168,7 +1226,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
@@ -1176,7 +1234,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>45215</v>
       </c>
       <c r="C5" t="s">
@@ -1184,12 +1242,12 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>45216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
@@ -1200,7 +1258,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>45218</v>
       </c>
       <c r="C8" t="s">
@@ -1208,7 +1266,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>45219</v>
       </c>
       <c r="C9" t="s">
@@ -1216,7 +1274,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
@@ -1224,7 +1282,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4">
+      <c r="A11" s="6">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
@@ -1232,7 +1290,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
@@ -1243,7 +1301,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="4">
+      <c r="A13" s="6">
         <v>45223</v>
       </c>
       <c r="C13" t="s">
@@ -1251,7 +1309,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="4">
+      <c r="A14" s="6">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
@@ -1259,7 +1317,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
@@ -1270,7 +1328,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
@@ -1280,28 +1338,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="4">
+    <row r="17" spans="1:3">
+      <c r="A17" s="6">
         <v>45227</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="4">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="6">
         <v>45228</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="4">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="6">
         <v>45229</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="4">
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="6">
         <v>45230</v>
       </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4">
+      <c r="A21" s="6">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
@@ -1312,7 +1394,7 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4">
+      <c r="A22" s="6">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
@@ -1323,7 +1405,7 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4">
+      <c r="A23" s="6">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
@@ -1334,7 +1416,7 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
@@ -1345,7 +1427,7 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4">
+      <c r="A25" s="6">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
@@ -1356,7 +1438,7 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4">
+      <c r="A26" s="6">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
@@ -1367,39 +1449,51 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4">
+      <c r="A27" s="6">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4">
+      <c r="A28" s="6">
         <v>45238</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4">
+      <c r="A29" s="6">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="4">
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="6">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4">
+      <c r="A31" s="6">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
@@ -1410,90 +1504,138 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4">
+      <c r="A32" s="6">
         <v>45242</v>
       </c>
-      <c r="C32" s="5"/>
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4">
+      <c r="A33" s="6">
         <v>45243</v>
       </c>
-      <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="4">
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="6">
         <v>45244</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="4">
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="6">
         <v>45245</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="4">
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="6">
         <v>45246</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="4">
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="6">
         <v>45247</v>
       </c>
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="4">
+      <c r="A38" s="6">
         <v>45248</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="4">
+      <c r="A39" s="6">
         <v>45249</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="4">
+    <row r="40" spans="1:3">
+      <c r="A40" s="6">
         <v>45250</v>
       </c>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="4">
+      <c r="A41" s="6">
         <v>45251</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="4">
+      <c r="A42" s="6">
         <v>45252</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="4">
+      <c r="A43" s="6">
         <v>45253</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="4">
+      <c r="A44" s="6">
         <v>45254</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="4">
+      <c r="A45" s="6">
         <v>45255</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="4">
+      <c r="A46" s="6">
         <v>45256</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="4">
+      <c r="A47" s="6">
         <v>45257</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="4">
+      <c r="A48" s="6">
         <v>45258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="6">
+        <v>45259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="6">
+        <v>45260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="6">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="6">
+        <v>45262</v>
       </c>
     </row>
   </sheetData>
@@ -1505,8 +1647,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -1516,16 +1658,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1538,49 +1694,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="1" max="2" width="11.5" style="4"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="B1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45255</v>
+      </c>
+      <c r="C2" s="4">
+        <v>45251</v>
+      </c>
+      <c r="D2" s="4">
+        <v>45252</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1596,226 +1746,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1831,6 +1981,56 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
@@ -1839,7 +2039,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -1880,36 +2080,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="2" width="11.5" style="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>45231</v>
-      </c>
-      <c r="B2" s="1">
-        <v>45249</v>
-      </c>
-      <c r="C2" s="1">
-        <v>45246</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
   <si>
     <t>生产日期</t>
   </si>
@@ -241,7 +241,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,13 +252,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -728,133 +721,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -875,7 +868,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -1562,9 +1555,12 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:3">
       <c r="A39" s="6">
         <v>45249</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1720,10 +1716,10 @@
         <v>45243</v>
       </c>
       <c r="B2" s="4">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="C2" s="4">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="D2" s="4">
         <v>45252</v>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -16,14 +16,29 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="90">
   <si>
     <t>生产日期</t>
   </si>
@@ -34,15 +49,24 @@
     <t>总装二线</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>跨月</t>
+  </si>
+  <si>
     <t>已完成</t>
   </si>
   <si>
-    <t>跨月</t>
-  </si>
-  <si>
     <t>无排产</t>
   </si>
   <si>
+    <t>澳洲车</t>
+  </si>
+  <si>
+    <t>展车</t>
+  </si>
+  <si>
     <t>物料编码</t>
   </si>
   <si>
@@ -55,16 +79,73 @@
     <t>不出原因</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>712W15101-0032</t>
   </si>
   <si>
     <t>SCR国V消音器总成</t>
   </si>
   <si>
-    <t>郭宝淇</t>
-  </si>
-  <si>
-    <t>互供物料，进入逆向</t>
+    <t>卢慧</t>
+  </si>
+  <si>
+    <t>互供物料，进入C39,指定潍柴，不出/1，5件</t>
+  </si>
+  <si>
+    <t>YG1674610021</t>
+  </si>
+  <si>
+    <t>左侧顶储物盒（NX-E/NX-G）</t>
+  </si>
+  <si>
+    <t>朱美芳</t>
+  </si>
+  <si>
+    <t>组合不出</t>
+  </si>
+  <si>
+    <t>YG1674610022</t>
+  </si>
+  <si>
+    <t>左侧顶储物盒骨架（NX-E/NX-G）</t>
+  </si>
+  <si>
+    <t>YG1674610033</t>
+  </si>
+  <si>
+    <t>右侧顶储物盒（NX-E/NX-G）</t>
+  </si>
+  <si>
+    <t>YG1674610034</t>
+  </si>
+  <si>
+    <t>右侧顶储物盒骨架（NX-E/NX-G）</t>
+  </si>
+  <si>
+    <t>YG9525771151</t>
+  </si>
+  <si>
+    <t>左门控制线束(NX/360环视)</t>
+  </si>
+  <si>
+    <t>陈新</t>
+  </si>
+  <si>
+    <t>走橡塑拉动</t>
+  </si>
+  <si>
+    <t>AZ992593128000</t>
+  </si>
+  <si>
+    <t>右踏板支架焊接总成</t>
+  </si>
+  <si>
+    <t>王凤玲</t>
+  </si>
+  <si>
+    <t>原包装少1件，3未锁帐</t>
   </si>
   <si>
     <t>起始日期</t>
@@ -94,7 +175,7 @@
     <t>312302.C02</t>
   </si>
   <si>
-    <t>收货</t>
+    <t>高位</t>
   </si>
   <si>
     <t>312302.C03</t>
@@ -232,16 +313,17 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]yyyy/mm/dd\ hh:mm\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -721,138 +811,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -868,8 +958,17 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1184,155 +1283,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:D138"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="3" width="8.875" customWidth="1"/>
     <col min="6" max="6" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6">
+      <c r="A2" s="9">
         <v>45212</v>
       </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>45213</v>
       </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>45215</v>
       </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
       <c r="C5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9">
         <v>45216</v>
       </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6">
+      <c r="A7" s="9">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="6">
+      <c r="A8" s="9">
         <v>45218</v>
       </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>45219</v>
       </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
       <c r="C9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="9">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="9">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="6">
+      <c r="A12" s="9">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="6">
+      <c r="A13" s="9">
         <v>45223</v>
       </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
       <c r="C13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="9">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="6">
+      <c r="A15" s="9">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="6">
+      <c r="A16" s="9">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="6">
+      <c r="A17" s="9">
         <v>45227</v>
       </c>
       <c r="B17" t="s">
@@ -1343,7 +1482,7 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="6">
+      <c r="A18" s="9">
         <v>45228</v>
       </c>
       <c r="B18" t="s">
@@ -1354,7 +1493,7 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6">
+      <c r="A19" s="9">
         <v>45229</v>
       </c>
       <c r="B19" t="s">
@@ -1365,7 +1504,7 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="6">
+      <c r="A20" s="9">
         <v>45230</v>
       </c>
       <c r="B20" t="s">
@@ -1376,266 +1515,1258 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="6">
+      <c r="A21" s="9">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="6">
+      <c r="A22" s="9">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="6">
+      <c r="A23" s="9">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="6">
+      <c r="A24" s="9">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="6">
+      <c r="A25" s="9">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="6">
+      <c r="A26" s="9">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="6">
+      <c r="A27" s="9">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="6">
+      <c r="A28" s="9">
         <v>45238</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="6">
+      <c r="A29" s="9">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="6">
+      <c r="A30" s="9">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="6">
+      <c r="A31" s="9">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="6">
+      <c r="A32" s="9">
         <v>45242</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="6">
+      <c r="A33" s="9">
         <v>45243</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="9">
         <v>45244</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="6">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="9">
         <v>45245</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="6">
+      <c r="A36" s="9">
         <v>45246</v>
       </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
       <c r="C36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="9">
         <v>45247</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="6">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="9">
         <v>45248</v>
       </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="6">
+      <c r="A39" s="9">
         <v>45249</v>
       </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
       <c r="C39" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="6">
+      <c r="A40" s="9">
         <v>45250</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="9">
         <v>45251</v>
       </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="6">
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="9">
         <v>45252</v>
       </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="6">
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="9">
         <v>45253</v>
       </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="6">
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="9">
         <v>45254</v>
       </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="6">
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="9">
         <v>45255</v>
       </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="6">
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="9">
         <v>45256</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="6">
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="9">
         <v>45257</v>
       </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="6">
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="9">
         <v>45258</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="6">
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="9">
         <v>45259</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="6">
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="9">
         <v>45260</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="6">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="9">
         <v>45261</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="6">
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="9">
         <v>45262</v>
       </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="9">
+        <v>45263</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="9">
+        <v>45264</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="9">
+        <v>45265</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="9">
+        <v>45266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="9">
+        <v>45267</v>
+      </c>
+      <c r="B57" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="9">
+        <v>45268</v>
+      </c>
+      <c r="B58" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="9">
+        <v>45269</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="9">
+        <v>45270</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="9">
+        <v>45271</v>
+      </c>
+      <c r="B61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="9">
+        <v>45272</v>
+      </c>
+      <c r="B62" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="9">
+        <v>45273</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="9">
+        <v>45274</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="9">
+        <v>45275</v>
+      </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="9">
+        <v>45276</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="9">
+        <v>45277</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="9">
+        <v>45278</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="9">
+        <v>45279</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="9">
+        <v>45280</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="9">
+        <v>45281</v>
+      </c>
+      <c r="B71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="9">
+        <v>45282</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="9">
+        <v>45283</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="9">
+        <v>45284</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="9">
+        <v>45285</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="9">
+        <v>45286</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="9">
+        <v>45287</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="9">
+        <v>45288</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="9">
+        <v>45289</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="9">
+        <v>45290</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="9">
+        <v>45291</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="9">
+        <v>45292</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="9">
+        <v>45293</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="9">
+        <v>45294</v>
+      </c>
+      <c r="B84" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="9">
+        <v>45295</v>
+      </c>
+      <c r="B85" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="9">
+        <v>45296</v>
+      </c>
+      <c r="B86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="9">
+        <v>45297</v>
+      </c>
+      <c r="B87" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="9">
+        <v>45298</v>
+      </c>
+      <c r="B88" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="9">
+        <v>45299</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="9">
+        <v>45300</v>
+      </c>
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="9">
+        <v>45301</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="9">
+        <v>45302</v>
+      </c>
+      <c r="B92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="9">
+        <v>45303</v>
+      </c>
+      <c r="B93" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="9">
+        <v>45304</v>
+      </c>
+      <c r="B94" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="9">
+        <v>45305</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="9">
+        <v>45306</v>
+      </c>
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="9">
+        <v>45307</v>
+      </c>
+      <c r="B97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="9">
+        <v>45308</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="9">
+        <v>45309</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="9">
+        <v>45310</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="9">
+        <v>45311</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="9">
+        <v>45312</v>
+      </c>
+      <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="9">
+        <v>45313</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="9">
+        <v>45314</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="9">
+        <v>45315</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="9">
+        <v>45316</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="9">
+        <v>45317</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="9">
+        <v>45318</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="9">
+        <v>45319</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="9">
+        <v>45320</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="9">
+        <v>45321</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="9">
+        <v>45322</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="9">
+        <v>45323</v>
+      </c>
+      <c r="B113" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="9">
+        <v>45324</v>
+      </c>
+      <c r="B114" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="9">
+        <v>45325</v>
+      </c>
+      <c r="B115" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="9">
+        <v>45326</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="9">
+        <v>45327</v>
+      </c>
+      <c r="B117" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="9">
+        <v>45328</v>
+      </c>
+      <c r="B118" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="9">
+        <v>45329</v>
+      </c>
+      <c r="B119" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="9">
+        <v>45330</v>
+      </c>
+      <c r="B120" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="9">
+        <v>45331</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="9">
+        <v>45332</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="9">
+        <v>45333</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="9">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="9">
+        <v>45335</v>
+      </c>
+      <c r="B125" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="9">
+        <v>45336</v>
+      </c>
+      <c r="B126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="9">
+        <v>45337</v>
+      </c>
+      <c r="B127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="9">
+        <v>45338</v>
+      </c>
+      <c r="B128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="9">
+        <v>45339</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="9">
+        <v>45340</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9">
+        <v>45341</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="9">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="9">
+        <v>45343</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="9">
+        <v>45344</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="9">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="9">
+        <v>45346</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="9">
+        <v>45347</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="9">
+        <v>45348</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D135">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1643,44 +2774,156 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="24.625" customWidth="1"/>
+    <col min="4" max="4" width="56.25" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="E2" s="5">
+        <v>45260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="5">
+        <v>45328.6316550926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="5">
+        <v>45343.408587963</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E7">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1699,34 +2942,35 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4">
-        <v>45243</v>
+        <v>45334</v>
       </c>
       <c r="B2" s="4">
-        <v>45256</v>
+        <v>45347</v>
       </c>
       <c r="C2" s="4">
-        <v>45252</v>
+        <v>45342</v>
       </c>
       <c r="D2" s="4">
-        <v>45252</v>
+        <v>45342</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1742,226 +2986,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1985,37 +3229,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2035,7 +3279,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -2087,37 +3331,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -16,8 +16,8 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="96">
   <si>
     <t>生产日期</t>
   </si>
@@ -136,16 +136,34 @@
     <t>走橡塑拉动</t>
   </si>
   <si>
-    <t>AZ992593128000</t>
-  </si>
-  <si>
-    <t>右踏板支架焊接总成</t>
+    <t>WG9925191211</t>
+  </si>
+  <si>
+    <t>油滤器支架总成</t>
   </si>
   <si>
     <t>王凤玲</t>
   </si>
   <si>
-    <t>原包装少1件，3未锁帐</t>
+    <t>49未锁帐</t>
+  </si>
+  <si>
+    <t>YZ952536000034</t>
+  </si>
+  <si>
+    <t>铝合金储气筒总成Φ276/30L</t>
+  </si>
+  <si>
+    <t>全部从26号开始出</t>
+  </si>
+  <si>
+    <t>AZ992552000005</t>
+  </si>
+  <si>
+    <t>减震器支架总成</t>
+  </si>
+  <si>
+    <t>陈玉文</t>
   </si>
   <si>
     <t>起始日期</t>
@@ -1283,7 +1301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -2683,19 +2701,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:3">
       <c r="A127" s="9">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="9">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2709,14 +2733,26 @@
         <v>45340</v>
       </c>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:3">
       <c r="A131" s="9">
         <v>45341</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="9">
         <v>45342</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -2761,8 +2797,39 @@
         <v>45348</v>
       </c>
     </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="9">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="9">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="9">
+        <v>45351</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="9">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="9">
+        <v>45353</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D135">
+  <autoFilter ref="A1:D143">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2774,8 +2841,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -2917,11 +2984,39 @@
         <v>35</v>
       </c>
       <c r="E8" s="5">
-        <v>45343.408587963</v>
+        <v>45345.6123611111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5">
+        <v>45345.70375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E7">
+  <autoFilter ref="A1:E9">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2942,16 +3037,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2959,13 +3054,13 @@
         <v>45334</v>
       </c>
       <c r="B2" s="4">
-        <v>45347</v>
+        <v>45352</v>
       </c>
       <c r="C2" s="4">
-        <v>45342</v>
+        <v>45348</v>
       </c>
       <c r="D2" s="4">
-        <v>45342</v>
+        <v>45348</v>
       </c>
     </row>
   </sheetData>
@@ -2986,226 +3081,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3229,37 +3324,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -3279,7 +3374,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -3331,37 +3426,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3016,7 +3016,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9">
+  <autoFilter ref="A1:E10">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -16,7 +16,7 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="86">
   <si>
     <t>生产日期</t>
   </si>
@@ -134,18 +134,6 @@
   </si>
   <si>
     <t>走橡塑拉动</t>
-  </si>
-  <si>
-    <t>AZ992593128000</t>
-  </si>
-  <si>
-    <t>右踏板支架焊接总成</t>
-  </si>
-  <si>
-    <t>王凤玲</t>
-  </si>
-  <si>
-    <t>原包装少1件，3未锁帐</t>
   </si>
   <si>
     <t>起始日期</t>
@@ -1283,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -2659,9 +2647,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:3">
       <c r="A124" s="9">
         <v>45334</v>
+      </c>
+      <c r="B124" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2683,40 +2677,67 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:3">
       <c r="A127" s="9">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="9">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:1">
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="9">
         <v>45339</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
+      <c r="C129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
       <c r="A130" s="9">
         <v>45340</v>
       </c>
-    </row>
-    <row r="131" spans="1:1">
+      <c r="B130" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
       <c r="A131" s="9">
         <v>45341</v>
       </c>
-    </row>
-    <row r="132" spans="1:1">
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="9">
         <v>45342</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -2761,8 +2782,76 @@
         <v>45348</v>
       </c>
     </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="9">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="9">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="9">
+        <v>45351</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="9">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="9">
+        <v>45353</v>
+      </c>
+      <c r="B143" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="9">
+        <v>45354</v>
+      </c>
+      <c r="B144" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="9">
+        <v>45355</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="9">
+        <v>45356</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="9">
+        <v>45357</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="9">
+        <v>45358</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D135">
+  <autoFilter ref="A1:D148">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2774,8 +2863,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -2901,23 +2990,6 @@
       </c>
       <c r="E7" s="5">
         <v>45328.6316550926</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5">
-        <v>45343.408587963</v>
       </c>
     </row>
   </sheetData>
@@ -2942,30 +3014,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4">
-        <v>45334</v>
+        <v>45349</v>
       </c>
       <c r="B2" s="4">
-        <v>45347</v>
+        <v>45358</v>
       </c>
       <c r="C2" s="4">
-        <v>45342</v>
+        <v>45355</v>
       </c>
       <c r="D2" s="4">
-        <v>45342</v>
+        <v>45355</v>
       </c>
     </row>
   </sheetData>
@@ -2986,226 +3058,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3229,37 +3301,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3279,7 +3351,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -3331,37 +3403,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -16,8 +16,8 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$D$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$F$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="89">
   <si>
     <t>生产日期</t>
   </si>
@@ -49,6 +49,12 @@
     <t>总装二线</t>
   </si>
   <si>
+    <t>一线跨</t>
+  </si>
+  <si>
+    <t>二线跨</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -58,6 +64,9 @@
     <t>已完成</t>
   </si>
   <si>
+    <t>全部</t>
+  </si>
+  <si>
     <t>无排产</t>
   </si>
   <si>
@@ -134,36 +143,6 @@
   </si>
   <si>
     <t>走橡塑拉动</t>
-  </si>
-  <si>
-    <t>WG9925191211</t>
-  </si>
-  <si>
-    <t>油滤器支架总成</t>
-  </si>
-  <si>
-    <t>王凤玲</t>
-  </si>
-  <si>
-    <t>49未锁帐</t>
-  </si>
-  <si>
-    <t>YZ952536000034</t>
-  </si>
-  <si>
-    <t>铝合金储气筒总成Φ276/30L</t>
-  </si>
-  <si>
-    <t>全部从26号开始出</t>
-  </si>
-  <si>
-    <t>AZ992552000005</t>
-  </si>
-  <si>
-    <t>减震器支架总成</t>
-  </si>
-  <si>
-    <t>陈玉文</t>
   </si>
   <si>
     <t>起始日期</t>
@@ -1301,15 +1280,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D143"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F148"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="3" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="11.5"/>
+    <col min="2" max="5" width="8.875" customWidth="1"/>
+    <col min="8" max="8" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1322,1514 +1301,2449 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="9">
         <v>45212</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="9">
         <v>45213</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="9">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="9">
         <v>45215</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="9">
         <v>45216</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="9">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="9">
         <v>45218</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="9">
         <v>45219</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="9">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="9">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="9">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="9">
         <v>45223</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="9">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="9">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="9">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="9">
         <v>45227</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="9">
         <v>45228</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="9">
         <v>45229</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="9">
         <v>45230</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="9">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="9">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="9">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="9">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="9">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="9">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="9">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="9">
         <v>45238</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="9">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="9">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="9">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="9">
         <v>45242</v>
       </c>
       <c r="B32" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="9">
         <v>45243</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="9">
         <v>45244</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="9">
         <v>45245</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="9">
         <v>45246</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="9">
         <v>45247</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="9">
         <v>45248</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="9">
         <v>45249</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="9">
         <v>45250</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="9">
         <v>45251</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="9">
         <v>45252</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="9">
         <v>45253</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="9">
         <v>45254</v>
       </c>
       <c r="B44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="9">
         <v>45255</v>
       </c>
       <c r="B45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="9">
         <v>45256</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="9">
         <v>45257</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="9">
         <v>45258</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="9">
         <v>45259</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="9">
         <v>45260</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="9">
         <v>45261</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="9">
         <v>45262</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="9">
         <v>45263</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="9">
         <v>45264</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="9">
         <v>45265</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="9">
         <v>45266</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="9">
         <v>45267</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="9">
         <v>45268</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="9">
         <v>45269</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="9">
         <v>45270</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" s="9">
         <v>45271</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" s="9">
         <v>45272</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" s="9">
         <v>45273</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D63" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" s="9">
         <v>45274</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="9">
         <v>45275</v>
       </c>
       <c r="B65" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D65" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="9">
         <v>45276</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="9">
         <v>45277</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="9">
         <v>45278</v>
       </c>
       <c r="B68" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" s="9">
         <v>45279</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" s="9">
         <v>45280</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" s="9">
         <v>45281</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" s="9">
         <v>45282</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="9">
         <v>45283</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="9">
         <v>45284</v>
       </c>
       <c r="B74" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" s="9">
         <v>45285</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" s="9">
         <v>45286</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" s="9">
         <v>45287</v>
       </c>
       <c r="B77" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" s="9">
         <v>45288</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" s="9">
         <v>45289</v>
       </c>
       <c r="B79" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" s="9">
         <v>45290</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="9">
         <v>45291</v>
       </c>
       <c r="B81" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D81" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="9">
         <v>45292</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="9">
         <v>45293</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="9">
         <v>45294</v>
       </c>
       <c r="B84" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" s="9">
         <v>45295</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" s="9">
         <v>45296</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="9">
         <v>45297</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D87" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" s="9">
         <v>45298</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="9">
         <v>45299</v>
       </c>
       <c r="B89" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C89" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="9">
         <v>45300</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="9">
         <v>45301</v>
       </c>
       <c r="B91" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" s="9">
         <v>45302</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D92" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" s="9">
         <v>45303</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D93" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" s="9">
         <v>45304</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="9">
         <v>45305</v>
       </c>
       <c r="B95" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" s="9">
         <v>45306</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D96" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" s="9">
         <v>45307</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="9">
         <v>45308</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" s="9">
         <v>45309</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" s="9">
         <v>45310</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="9">
         <v>45311</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" s="9">
         <v>45312</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" s="9">
         <v>45313</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" s="9">
         <v>45314</v>
       </c>
       <c r="B104" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" s="9">
         <v>45315</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D105" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" s="9">
         <v>45316</v>
       </c>
       <c r="B106" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" s="9">
         <v>45317</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="9">
         <v>45318</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C108" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="9">
         <v>45319</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C109" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D109" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" s="9">
         <v>45320</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C110" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D110" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" s="9">
         <v>45321</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C111" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" s="9">
         <v>45322</v>
       </c>
       <c r="B112" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D112" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" s="9">
         <v>45323</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" s="9">
         <v>45324</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" s="9">
         <v>45325</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" s="9">
         <v>45326</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D116" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" s="9">
         <v>45327</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>8</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" s="9">
         <v>45328</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" s="9">
         <v>45329</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" s="9">
         <v>45330</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="9">
         <v>45331</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="E121" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" s="9">
         <v>45332</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D122" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" s="9">
         <v>45333</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" s="9">
         <v>45334</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="B124" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" s="9">
         <v>45335</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="D125" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" s="9">
         <v>45336</v>
       </c>
       <c r="B126" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="C126" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" s="9">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D127" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" s="9">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
+        <v>7</v>
+      </c>
+      <c r="D128" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" s="9">
         <v>45339</v>
       </c>
-    </row>
-    <row r="130" spans="1:1">
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" s="9">
         <v>45340</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="B130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" s="9">
         <v>45341</v>
       </c>
       <c r="B131" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D131" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" s="9">
         <v>45342</v>
       </c>
       <c r="B132" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
+        <v>7</v>
+      </c>
+      <c r="D132" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" s="9">
         <v>45343</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" s="9">
         <v>45344</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="D134" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="9">
         <v>45345</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" s="9">
         <v>45346</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="D136" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" s="9">
         <v>45347</v>
       </c>
-    </row>
-    <row r="138" spans="1:1">
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" s="9">
         <v>45348</v>
       </c>
-    </row>
-    <row r="139" spans="1:1">
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" s="9">
         <v>45349</v>
       </c>
-    </row>
-    <row r="140" spans="1:1">
+      <c r="B139"/>
+      <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" s="9">
         <v>45350</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="D140" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" s="9">
         <v>45351</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
+        <v>9</v>
+      </c>
+      <c r="D141" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" s="9">
         <v>45352</v>
       </c>
-    </row>
-    <row r="143" spans="1:1">
+      <c r="D142" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="9">
         <v>45353</v>
       </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="9">
+        <v>45354</v>
+      </c>
+      <c r="B144" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="9">
+        <v>45355</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="9">
+        <v>45356</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="9">
+        <v>45357</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="9">
+        <v>45358</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D143">
+  <autoFilter ref="A1:F148">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2841,8 +3755,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -2853,33 +3767,33 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="5">
         <v>45260</v>
@@ -2887,16 +3801,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="5">
         <v>45318.4237731481</v>
@@ -2904,16 +3818,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5">
         <v>45318.4237731481</v>
@@ -2921,16 +3835,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
       </c>
       <c r="E5" s="5">
         <v>45318.4237731481</v>
@@ -2938,16 +3852,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="5">
         <v>45318.4237731481</v>
@@ -2955,68 +3869,23 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7" s="5">
         <v>45328.6316550926</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="5">
-        <v>45345.6123611111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="5">
-        <v>45345.70375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E10">
+  <autoFilter ref="A1:E7">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3037,30 +3906,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4">
-        <v>45334</v>
+        <v>45349</v>
       </c>
       <c r="B2" s="4">
-        <v>45352</v>
+        <v>45358</v>
       </c>
       <c r="C2" s="4">
-        <v>45348</v>
+        <v>45355</v>
       </c>
       <c r="D2" s="4">
-        <v>45348</v>
+        <v>45355</v>
       </c>
     </row>
   </sheetData>
@@ -3081,226 +3950,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3324,37 +4193,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3374,7 +4243,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -3426,37 +4295,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -7,18 +7,17 @@
     <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2"/>
   </bookViews>
   <sheets>
-    <sheet name="排产完成状况表" sheetId="5" r:id="rId1"/>
+    <sheet name="排产状况表" sheetId="5" r:id="rId1"/>
     <sheet name="临时不出库物料表" sheetId="7" r:id="rId2"/>
-    <sheet name="日期配置" sheetId="8" r:id="rId3"/>
-    <sheet name="库区表" sheetId="1" r:id="rId4"/>
-    <sheet name="不出库库区表" sheetId="6" r:id="rId5"/>
-    <sheet name="不出库供应商表" sheetId="4" r:id="rId6"/>
-    <sheet name="分装工位表" sheetId="9" r:id="rId7"/>
+    <sheet name="库区表" sheetId="1" r:id="rId3"/>
+    <sheet name="不出库库区表" sheetId="6" r:id="rId4"/>
+    <sheet name="不出库供应商表" sheetId="4" r:id="rId5"/>
+    <sheet name="分装工位表" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产完成状况表!$A$1:$F$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产状况表!$A$1:$F$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">库区表!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,15 +37,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="85">
   <si>
     <t>生产日期</t>
   </si>
   <si>
-    <t>总装一线</t>
-  </si>
-  <si>
-    <t>总装二线</t>
+    <t>一线完成情况</t>
+  </si>
+  <si>
+    <t>二线完成情况</t>
   </si>
   <si>
     <t>一线跨</t>
@@ -143,18 +142,6 @@
   </si>
   <si>
     <t>走橡塑拉动</t>
-  </si>
-  <si>
-    <t>起始日期</t>
-  </si>
-  <si>
-    <t>截止日期</t>
-  </si>
-  <si>
-    <t>跨分拣截止日期</t>
-  </si>
-  <si>
-    <t>跨分装截止日期</t>
   </si>
   <si>
     <t>库区编码</t>
@@ -311,14 +298,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]yyyy/mm/dd\ hh:mm\ AM/PM;@"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="[$-409]yyyy/mm/dd\ hh:mm\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -955,18 +941,18 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1283,33 +1269,35 @@
   <dimension ref="A1:F148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="5" width="8.875" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="8" customWidth="1"/>
+    <col min="2" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="5" width="7.375" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
     <col min="8" max="8" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>45212</v>
       </c>
       <c r="B2" t="s">
@@ -1326,7 +1314,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>45213</v>
       </c>
       <c r="B3" t="s">
@@ -1343,7 +1331,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
@@ -1360,7 +1348,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>45215</v>
       </c>
       <c r="B5" t="s">
@@ -1377,7 +1365,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>45216</v>
       </c>
       <c r="B6" t="s">
@@ -1394,7 +1382,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
@@ -1411,7 +1399,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>45218</v>
       </c>
       <c r="B8" t="s">
@@ -1428,7 +1416,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>45219</v>
       </c>
       <c r="B9" t="s">
@@ -1445,7 +1433,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
@@ -1462,7 +1450,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
@@ -1479,7 +1467,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
@@ -1496,7 +1484,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>45223</v>
       </c>
       <c r="B13" t="s">
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
@@ -1530,7 +1518,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
@@ -1547,7 +1535,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
@@ -1564,7 +1552,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>45227</v>
       </c>
       <c r="B17" t="s">
@@ -1581,7 +1569,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>45228</v>
       </c>
       <c r="B18" t="s">
@@ -1598,7 +1586,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>45229</v>
       </c>
       <c r="B19" t="s">
@@ -1615,7 +1603,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>45230</v>
       </c>
       <c r="B20" t="s">
@@ -1632,7 +1620,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
@@ -1649,7 +1637,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
@@ -1666,7 +1654,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
@@ -1683,7 +1671,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
@@ -1700,7 +1688,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
@@ -1717,7 +1705,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="9">
+      <c r="A26" s="8">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
@@ -1734,7 +1722,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
@@ -1751,7 +1739,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>45238</v>
       </c>
       <c r="B28" t="s">
@@ -1768,7 +1756,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="9">
+      <c r="A30" s="8">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
@@ -1802,7 +1790,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
@@ -1819,7 +1807,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>45242</v>
       </c>
       <c r="B32" t="s">
@@ -1836,7 +1824,7 @@
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>45243</v>
       </c>
       <c r="B33" t="s">
@@ -1853,7 +1841,7 @@
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>45244</v>
       </c>
       <c r="B34" t="s">
@@ -1870,7 +1858,7 @@
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>45245</v>
       </c>
       <c r="B35" t="s">
@@ -1887,7 +1875,7 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>45246</v>
       </c>
       <c r="B36" t="s">
@@ -1904,7 +1892,7 @@
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="9">
+      <c r="A37" s="8">
         <v>45247</v>
       </c>
       <c r="B37" t="s">
@@ -1921,7 +1909,7 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="9">
+      <c r="A38" s="8">
         <v>45248</v>
       </c>
       <c r="B38" t="s">
@@ -1938,7 +1926,7 @@
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="9">
+      <c r="A39" s="8">
         <v>45249</v>
       </c>
       <c r="B39" t="s">
@@ -1955,7 +1943,7 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="9">
+      <c r="A40" s="8">
         <v>45250</v>
       </c>
       <c r="B40" t="s">
@@ -1972,7 +1960,7 @@
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>45251</v>
       </c>
       <c r="B41" t="s">
@@ -1989,7 +1977,7 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>45252</v>
       </c>
       <c r="B42" t="s">
@@ -2006,7 +1994,7 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>45253</v>
       </c>
       <c r="B43" t="s">
@@ -2023,7 +2011,7 @@
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>45254</v>
       </c>
       <c r="B44" t="s">
@@ -2040,7 +2028,7 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>45255</v>
       </c>
       <c r="B45" t="s">
@@ -2057,7 +2045,7 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="9">
+      <c r="A46" s="8">
         <v>45256</v>
       </c>
       <c r="B46" t="s">
@@ -2074,7 +2062,7 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="9">
+      <c r="A47" s="8">
         <v>45257</v>
       </c>
       <c r="B47" t="s">
@@ -2091,7 +2079,7 @@
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="9">
+      <c r="A48" s="8">
         <v>45258</v>
       </c>
       <c r="B48" t="s">
@@ -2108,7 +2096,7 @@
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="9">
+      <c r="A49" s="8">
         <v>45259</v>
       </c>
       <c r="B49" t="s">
@@ -2125,7 +2113,7 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="9">
+      <c r="A50" s="8">
         <v>45260</v>
       </c>
       <c r="B50" t="s">
@@ -2142,7 +2130,7 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="9">
+      <c r="A51" s="8">
         <v>45261</v>
       </c>
       <c r="B51" t="s">
@@ -2159,7 +2147,7 @@
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="9">
+      <c r="A52" s="8">
         <v>45262</v>
       </c>
       <c r="B52" t="s">
@@ -2176,7 +2164,7 @@
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>45263</v>
       </c>
       <c r="B53" t="s">
@@ -2193,7 +2181,7 @@
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>45264</v>
       </c>
       <c r="B54" t="s">
@@ -2210,7 +2198,7 @@
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="9">
+      <c r="A55" s="8">
         <v>45265</v>
       </c>
       <c r="B55" t="s">
@@ -2227,7 +2215,7 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>45266</v>
       </c>
       <c r="B56" t="s">
@@ -2244,7 +2232,7 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>45267</v>
       </c>
       <c r="B57" t="s">
@@ -2261,7 +2249,7 @@
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="9">
+      <c r="A58" s="8">
         <v>45268</v>
       </c>
       <c r="B58" t="s">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>45269</v>
       </c>
       <c r="B59" t="s">
@@ -2295,7 +2283,7 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>45270</v>
       </c>
       <c r="B60" t="s">
@@ -2315,7 +2303,7 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>45271</v>
       </c>
       <c r="B61" t="s">
@@ -2332,7 +2320,7 @@
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>45272</v>
       </c>
       <c r="B62" t="s">
@@ -2349,7 +2337,7 @@
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>45273</v>
       </c>
       <c r="B63" t="s">
@@ -2366,7 +2354,7 @@
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="9">
+      <c r="A64" s="8">
         <v>45274</v>
       </c>
       <c r="B64" t="s">
@@ -2383,7 +2371,7 @@
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="9">
+      <c r="A65" s="8">
         <v>45275</v>
       </c>
       <c r="B65" t="s">
@@ -2400,7 +2388,7 @@
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="9">
+      <c r="A66" s="8">
         <v>45276</v>
       </c>
       <c r="B66" t="s">
@@ -2417,7 +2405,7 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="9">
+      <c r="A67" s="8">
         <v>45277</v>
       </c>
       <c r="B67" t="s">
@@ -2434,7 +2422,7 @@
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="9">
+      <c r="A68" s="8">
         <v>45278</v>
       </c>
       <c r="B68" t="s">
@@ -2451,7 +2439,7 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>45279</v>
       </c>
       <c r="B69" t="s">
@@ -2468,7 +2456,7 @@
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>45280</v>
       </c>
       <c r="B70" t="s">
@@ -2485,7 +2473,7 @@
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>45281</v>
       </c>
       <c r="B71" t="s">
@@ -2502,7 +2490,7 @@
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>45282</v>
       </c>
       <c r="B72" t="s">
@@ -2519,7 +2507,7 @@
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="9">
+      <c r="A73" s="8">
         <v>45283</v>
       </c>
       <c r="B73" t="s">
@@ -2536,7 +2524,7 @@
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="9">
+      <c r="A74" s="8">
         <v>45284</v>
       </c>
       <c r="B74" t="s">
@@ -2553,7 +2541,7 @@
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="9">
+      <c r="A75" s="8">
         <v>45285</v>
       </c>
       <c r="B75" t="s">
@@ -2570,7 +2558,7 @@
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="9">
+      <c r="A76" s="8">
         <v>45286</v>
       </c>
       <c r="B76" t="s">
@@ -2587,7 +2575,7 @@
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="9">
+      <c r="A77" s="8">
         <v>45287</v>
       </c>
       <c r="B77" t="s">
@@ -2604,7 +2592,7 @@
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="9">
+      <c r="A78" s="8">
         <v>45288</v>
       </c>
       <c r="B78" t="s">
@@ -2621,7 +2609,7 @@
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="9">
+      <c r="A79" s="8">
         <v>45289</v>
       </c>
       <c r="B79" t="s">
@@ -2638,7 +2626,7 @@
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="9">
+      <c r="A80" s="8">
         <v>45290</v>
       </c>
       <c r="B80" t="s">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="9">
+      <c r="A81" s="8">
         <v>45291</v>
       </c>
       <c r="B81" t="s">
@@ -2672,7 +2660,7 @@
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="9">
+      <c r="A82" s="8">
         <v>45292</v>
       </c>
       <c r="B82" t="s">
@@ -2689,7 +2677,7 @@
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="9">
+      <c r="A83" s="8">
         <v>45293</v>
       </c>
       <c r="B83" t="s">
@@ -2706,7 +2694,7 @@
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="9">
+      <c r="A84" s="8">
         <v>45294</v>
       </c>
       <c r="B84" t="s">
@@ -2726,7 +2714,7 @@
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="9">
+      <c r="A85" s="8">
         <v>45295</v>
       </c>
       <c r="B85" t="s">
@@ -2743,7 +2731,7 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="9">
+      <c r="A86" s="8">
         <v>45296</v>
       </c>
       <c r="B86" t="s">
@@ -2760,7 +2748,7 @@
       </c>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="9">
+      <c r="A87" s="8">
         <v>45297</v>
       </c>
       <c r="B87" t="s">
@@ -2777,7 +2765,7 @@
       </c>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="9">
+      <c r="A88" s="8">
         <v>45298</v>
       </c>
       <c r="B88" t="s">
@@ -2794,7 +2782,7 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="9">
+      <c r="A89" s="8">
         <v>45299</v>
       </c>
       <c r="B89" t="s">
@@ -2811,7 +2799,7 @@
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="9">
+      <c r="A90" s="8">
         <v>45300</v>
       </c>
       <c r="B90" t="s">
@@ -2828,7 +2816,7 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="9">
+      <c r="A91" s="8">
         <v>45301</v>
       </c>
       <c r="B91" t="s">
@@ -2845,7 +2833,7 @@
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="9">
+      <c r="A92" s="8">
         <v>45302</v>
       </c>
       <c r="B92" t="s">
@@ -2862,7 +2850,7 @@
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="9">
+      <c r="A93" s="8">
         <v>45303</v>
       </c>
       <c r="B93" t="s">
@@ -2879,7 +2867,7 @@
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="9">
+      <c r="A94" s="8">
         <v>45304</v>
       </c>
       <c r="B94" t="s">
@@ -2896,7 +2884,7 @@
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="9">
+      <c r="A95" s="8">
         <v>45305</v>
       </c>
       <c r="B95" t="s">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="9">
+      <c r="A96" s="8">
         <v>45306</v>
       </c>
       <c r="B96" t="s">
@@ -2933,7 +2921,7 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="9">
+      <c r="A97" s="8">
         <v>45307</v>
       </c>
       <c r="B97" t="s">
@@ -2950,7 +2938,7 @@
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="9">
+      <c r="A98" s="8">
         <v>45308</v>
       </c>
       <c r="B98" t="s">
@@ -2967,7 +2955,7 @@
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="9">
+      <c r="A99" s="8">
         <v>45309</v>
       </c>
       <c r="B99" t="s">
@@ -2984,7 +2972,7 @@
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="9">
+      <c r="A100" s="8">
         <v>45310</v>
       </c>
       <c r="B100" t="s">
@@ -3001,7 +2989,7 @@
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="9">
+      <c r="A101" s="8">
         <v>45311</v>
       </c>
       <c r="B101" t="s">
@@ -3018,7 +3006,7 @@
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="9">
+      <c r="A102" s="8">
         <v>45312</v>
       </c>
       <c r="B102" t="s">
@@ -3035,7 +3023,7 @@
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="9">
+      <c r="A103" s="8">
         <v>45313</v>
       </c>
       <c r="B103" t="s">
@@ -3052,7 +3040,7 @@
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="9">
+      <c r="A104" s="8">
         <v>45314</v>
       </c>
       <c r="B104" t="s">
@@ -3069,7 +3057,7 @@
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="9">
+      <c r="A105" s="8">
         <v>45315</v>
       </c>
       <c r="B105" t="s">
@@ -3086,7 +3074,7 @@
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="9">
+      <c r="A106" s="8">
         <v>45316</v>
       </c>
       <c r="B106" t="s">
@@ -3103,7 +3091,7 @@
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="9">
+      <c r="A107" s="8">
         <v>45317</v>
       </c>
       <c r="B107" t="s">
@@ -3120,7 +3108,7 @@
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="9">
+      <c r="A108" s="8">
         <v>45318</v>
       </c>
       <c r="B108" t="s">
@@ -3137,7 +3125,7 @@
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="9">
+      <c r="A109" s="8">
         <v>45319</v>
       </c>
       <c r="B109" t="s">
@@ -3154,7 +3142,7 @@
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="9">
+      <c r="A110" s="8">
         <v>45320</v>
       </c>
       <c r="B110" t="s">
@@ -3171,7 +3159,7 @@
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="9">
+      <c r="A111" s="8">
         <v>45321</v>
       </c>
       <c r="B111" t="s">
@@ -3188,7 +3176,7 @@
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="9">
+      <c r="A112" s="8">
         <v>45322</v>
       </c>
       <c r="B112" t="s">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="9">
+      <c r="A113" s="8">
         <v>45323</v>
       </c>
       <c r="B113" t="s">
@@ -3222,7 +3210,7 @@
       </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="9">
+      <c r="A114" s="8">
         <v>45324</v>
       </c>
       <c r="B114" t="s">
@@ -3239,7 +3227,7 @@
       </c>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="9">
+      <c r="A115" s="8">
         <v>45325</v>
       </c>
       <c r="B115" t="s">
@@ -3256,7 +3244,7 @@
       </c>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="9">
+      <c r="A116" s="8">
         <v>45326</v>
       </c>
       <c r="B116" t="s">
@@ -3273,7 +3261,7 @@
       </c>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="9">
+      <c r="A117" s="8">
         <v>45327</v>
       </c>
       <c r="B117" t="s">
@@ -3290,7 +3278,7 @@
       </c>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="9">
+      <c r="A118" s="8">
         <v>45328</v>
       </c>
       <c r="B118" t="s">
@@ -3307,7 +3295,7 @@
       </c>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="9">
+      <c r="A119" s="8">
         <v>45329</v>
       </c>
       <c r="B119" t="s">
@@ -3324,7 +3312,7 @@
       </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="9">
+      <c r="A120" s="8">
         <v>45330</v>
       </c>
       <c r="B120" t="s">
@@ -3341,7 +3329,7 @@
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="9">
+      <c r="A121" s="8">
         <v>45331</v>
       </c>
       <c r="B121" t="s">
@@ -3361,7 +3349,7 @@
       </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="9">
+      <c r="A122" s="8">
         <v>45332</v>
       </c>
       <c r="B122" t="s">
@@ -3378,7 +3366,7 @@
       </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="9">
+      <c r="A123" s="8">
         <v>45333</v>
       </c>
       <c r="B123" t="s">
@@ -3395,7 +3383,7 @@
       </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="9">
+      <c r="A124" s="8">
         <v>45334</v>
       </c>
       <c r="B124" t="s">
@@ -3412,7 +3400,7 @@
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="9">
+      <c r="A125" s="8">
         <v>45335</v>
       </c>
       <c r="B125" t="s">
@@ -3429,7 +3417,7 @@
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="9">
+      <c r="A126" s="8">
         <v>45336</v>
       </c>
       <c r="B126" t="s">
@@ -3446,7 +3434,7 @@
       </c>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="9">
+      <c r="A127" s="8">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
@@ -3463,7 +3451,7 @@
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="9">
+      <c r="A128" s="8">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
@@ -3480,7 +3468,7 @@
       </c>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="9">
+      <c r="A129" s="8">
         <v>45339</v>
       </c>
       <c r="B129" t="s">
@@ -3497,7 +3485,7 @@
       </c>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="9">
+      <c r="A130" s="8">
         <v>45340</v>
       </c>
       <c r="B130" t="s">
@@ -3514,7 +3502,7 @@
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="9">
+      <c r="A131" s="8">
         <v>45341</v>
       </c>
       <c r="B131" t="s">
@@ -3531,7 +3519,7 @@
       </c>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="9">
+      <c r="A132" s="8">
         <v>45342</v>
       </c>
       <c r="B132" t="s">
@@ -3548,7 +3536,7 @@
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="9">
+      <c r="A133" s="8">
         <v>45343</v>
       </c>
       <c r="B133" t="s">
@@ -3565,7 +3553,7 @@
       </c>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="9">
+      <c r="A134" s="8">
         <v>45344</v>
       </c>
       <c r="B134" t="s">
@@ -3582,7 +3570,7 @@
       </c>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="9">
+      <c r="A135" s="8">
         <v>45345</v>
       </c>
       <c r="B135" t="s">
@@ -3599,7 +3587,7 @@
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="9">
+      <c r="A136" s="8">
         <v>45346</v>
       </c>
       <c r="B136" t="s">
@@ -3616,7 +3604,7 @@
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="9">
+      <c r="A137" s="8">
         <v>45347</v>
       </c>
       <c r="B137" t="s">
@@ -3633,7 +3621,7 @@
       </c>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="9">
+      <c r="A138" s="8">
         <v>45348</v>
       </c>
       <c r="B138" t="s">
@@ -3650,7 +3638,7 @@
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="9">
+      <c r="A139" s="8">
         <v>45349</v>
       </c>
       <c r="B139"/>
@@ -3662,7 +3650,7 @@
       </c>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="9">
+      <c r="A140" s="8">
         <v>45350</v>
       </c>
       <c r="D140" t="s">
@@ -3673,7 +3661,7 @@
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="9">
+      <c r="A141" s="8">
         <v>45351</v>
       </c>
       <c r="B141" t="s">
@@ -3690,7 +3678,7 @@
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="9">
+      <c r="A142" s="8">
         <v>45352</v>
       </c>
       <c r="D142" t="s">
@@ -3701,7 +3689,7 @@
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="9">
+      <c r="A143" s="8">
         <v>45353</v>
       </c>
       <c r="B143" t="s">
@@ -3712,7 +3700,7 @@
       </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="9">
+      <c r="A144" s="8">
         <v>45354</v>
       </c>
       <c r="B144" t="s">
@@ -3723,22 +3711,22 @@
       </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="9">
+      <c r="A145" s="8">
         <v>45355</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="9">
+      <c r="A146" s="8">
         <v>45356</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="9">
+      <c r="A147" s="8">
         <v>45357</v>
       </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="9">
+      <c r="A148" s="8">
         <v>45358</v>
       </c>
     </row>
@@ -3762,28 +3750,28 @@
     <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="56.25" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="5"/>
+    <col min="5" max="5" width="21.5" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
@@ -3795,7 +3783,7 @@
       <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>45260</v>
       </c>
     </row>
@@ -3812,7 +3800,7 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>45318.4237731481</v>
       </c>
     </row>
@@ -3829,7 +3817,7 @@
       <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>45318.4237731481</v>
       </c>
     </row>
@@ -3846,7 +3834,7 @@
       <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>45318.4237731481</v>
       </c>
     </row>
@@ -3863,7 +3851,7 @@
       <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>45318.4237731481</v>
       </c>
     </row>
@@ -3880,7 +3868,7 @@
       <c r="D7" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>45328.6316550926</v>
       </c>
     </row>
@@ -3897,51 +3885,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="2" width="11.5" style="4"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="4">
-        <v>45349</v>
-      </c>
-      <c r="B2" s="4">
-        <v>45358</v>
-      </c>
-      <c r="C2" s="4">
-        <v>45355</v>
-      </c>
-      <c r="D2" s="4">
-        <v>45355</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
@@ -3950,226 +3893,226 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4182,7 +4125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A7"/>
@@ -4193,37 +4136,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -4232,7 +4175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B7"/>
@@ -4243,7 +4186,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -4284,7 +4227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A7"/>
@@ -4295,37 +4238,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\SourceCode\Work-Chinapost\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA624A73-8685-407B-B0CC-65E5E0DAE02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" firstSheet="2"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排产状况表" sheetId="5" r:id="rId1"/>
@@ -15,9 +21,9 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">库区表!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产状况表!$A$1:$F$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">库区表!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="85">
   <si>
     <t>生产日期</t>
   </si>
@@ -297,16 +301,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-409]yyyy/mm/dd\ hh:mm\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +318,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -326,349 +327,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -676,254 +363,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -948,69 +393,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1260,24 +661,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F148"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F149"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="8" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="9" customWidth="1"/>
     <col min="2" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="5" width="7.375" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
     <col min="8" max="8" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1296,8 +697,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="8">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A2" s="9">
         <v>45212</v>
       </c>
       <c r="B2" t="s">
@@ -1313,8 +714,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="8">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="9">
         <v>45213</v>
       </c>
       <c r="B3" t="s">
@@ -1330,8 +731,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="8">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="9">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
@@ -1347,8 +748,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="8">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="9">
         <v>45215</v>
       </c>
       <c r="B5" t="s">
@@ -1364,8 +765,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="8">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A6" s="9">
         <v>45216</v>
       </c>
       <c r="B6" t="s">
@@ -1381,8 +782,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="8">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A7" s="9">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
@@ -1398,8 +799,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A8" s="9">
         <v>45218</v>
       </c>
       <c r="B8" t="s">
@@ -1415,8 +816,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="8">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A9" s="9">
         <v>45219</v>
       </c>
       <c r="B9" t="s">
@@ -1432,8 +833,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="8">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A10" s="9">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
@@ -1449,8 +850,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="8">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A11" s="9">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
@@ -1466,8 +867,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="8">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A12" s="9">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
@@ -1483,8 +884,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="8">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A13" s="9">
         <v>45223</v>
       </c>
       <c r="B13" t="s">
@@ -1500,8 +901,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="8">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A14" s="9">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
@@ -1517,8 +918,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="8">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A15" s="9">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
@@ -1534,8 +935,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="8">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A16" s="9">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
@@ -1551,8 +952,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="8">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="9">
         <v>45227</v>
       </c>
       <c r="B17" t="s">
@@ -1568,8 +969,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="8">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="9">
         <v>45228</v>
       </c>
       <c r="B18" t="s">
@@ -1585,8 +986,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="8">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="9">
         <v>45229</v>
       </c>
       <c r="B19" t="s">
@@ -1602,8 +1003,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="8">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="9">
         <v>45230</v>
       </c>
       <c r="B20" t="s">
@@ -1619,8 +1020,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="8">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="9">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
@@ -1636,8 +1037,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="8">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="9">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
@@ -1653,8 +1054,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="8">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="9">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
@@ -1670,8 +1071,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="8">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="9">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
@@ -1687,8 +1088,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="8">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="9">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
@@ -1704,8 +1105,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="8">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="9">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
@@ -1721,8 +1122,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="8">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="9">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
@@ -1738,8 +1139,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="8">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="9">
         <v>45238</v>
       </c>
       <c r="B28" t="s">
@@ -1755,8 +1156,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="8">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="9">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
@@ -1772,8 +1173,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="8">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="9">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
@@ -1789,8 +1190,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="9">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
@@ -1806,8 +1207,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="8">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="9">
         <v>45242</v>
       </c>
       <c r="B32" t="s">
@@ -1823,8 +1224,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="8">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="9">
         <v>45243</v>
       </c>
       <c r="B33" t="s">
@@ -1840,8 +1241,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="8">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="9">
         <v>45244</v>
       </c>
       <c r="B34" t="s">
@@ -1857,8 +1258,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="8">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="9">
         <v>45245</v>
       </c>
       <c r="B35" t="s">
@@ -1874,8 +1275,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="8">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="9">
         <v>45246</v>
       </c>
       <c r="B36" t="s">
@@ -1891,8 +1292,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="8">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="9">
         <v>45247</v>
       </c>
       <c r="B37" t="s">
@@ -1908,8 +1309,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="8">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="9">
         <v>45248</v>
       </c>
       <c r="B38" t="s">
@@ -1925,8 +1326,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="8">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="9">
         <v>45249</v>
       </c>
       <c r="B39" t="s">
@@ -1942,8 +1343,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="8">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40" s="9">
         <v>45250</v>
       </c>
       <c r="B40" t="s">
@@ -1959,8 +1360,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="8">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="9">
         <v>45251</v>
       </c>
       <c r="B41" t="s">
@@ -1976,8 +1377,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="8">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="9">
         <v>45252</v>
       </c>
       <c r="B42" t="s">
@@ -1993,8 +1394,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="8">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="9">
         <v>45253</v>
       </c>
       <c r="B43" t="s">
@@ -2010,8 +1411,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="8">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="9">
         <v>45254</v>
       </c>
       <c r="B44" t="s">
@@ -2027,8 +1428,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="8">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="9">
         <v>45255</v>
       </c>
       <c r="B45" t="s">
@@ -2044,8 +1445,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="8">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A46" s="9">
         <v>45256</v>
       </c>
       <c r="B46" t="s">
@@ -2061,8 +1462,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="8">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A47" s="9">
         <v>45257</v>
       </c>
       <c r="B47" t="s">
@@ -2078,8 +1479,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="8">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A48" s="9">
         <v>45258</v>
       </c>
       <c r="B48" t="s">
@@ -2095,8 +1496,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="8">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A49" s="9">
         <v>45259</v>
       </c>
       <c r="B49" t="s">
@@ -2112,8 +1513,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="8">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A50" s="9">
         <v>45260</v>
       </c>
       <c r="B50" t="s">
@@ -2129,8 +1530,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="8">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A51" s="9">
         <v>45261</v>
       </c>
       <c r="B51" t="s">
@@ -2146,8 +1547,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="8">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A52" s="9">
         <v>45262</v>
       </c>
       <c r="B52" t="s">
@@ -2163,8 +1564,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="8">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="9">
         <v>45263</v>
       </c>
       <c r="B53" t="s">
@@ -2180,8 +1581,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="8">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="9">
         <v>45264</v>
       </c>
       <c r="B54" t="s">
@@ -2197,8 +1598,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="8">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="9">
         <v>45265</v>
       </c>
       <c r="B55" t="s">
@@ -2214,8 +1615,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="8">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="9">
         <v>45266</v>
       </c>
       <c r="B56" t="s">
@@ -2231,8 +1632,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="8">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="9">
         <v>45267</v>
       </c>
       <c r="B57" t="s">
@@ -2248,8 +1649,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="8">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="9">
         <v>45268</v>
       </c>
       <c r="B58" t="s">
@@ -2265,8 +1666,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="8">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A59" s="9">
         <v>45269</v>
       </c>
       <c r="B59" t="s">
@@ -2282,8 +1683,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="8">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A60" s="9">
         <v>45270</v>
       </c>
       <c r="B60" t="s">
@@ -2302,8 +1703,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="8">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A61" s="9">
         <v>45271</v>
       </c>
       <c r="B61" t="s">
@@ -2319,8 +1720,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="8">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A62" s="9">
         <v>45272</v>
       </c>
       <c r="B62" t="s">
@@ -2336,8 +1737,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="8">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A63" s="9">
         <v>45273</v>
       </c>
       <c r="B63" t="s">
@@ -2353,8 +1754,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="8">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A64" s="9">
         <v>45274</v>
       </c>
       <c r="B64" t="s">
@@ -2370,8 +1771,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="8">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65" s="9">
         <v>45275</v>
       </c>
       <c r="B65" t="s">
@@ -2387,8 +1788,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="8">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66" s="9">
         <v>45276</v>
       </c>
       <c r="B66" t="s">
@@ -2404,8 +1805,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="8">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67" s="9">
         <v>45277</v>
       </c>
       <c r="B67" t="s">
@@ -2421,8 +1822,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="8">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="9">
         <v>45278</v>
       </c>
       <c r="B68" t="s">
@@ -2438,8 +1839,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="8">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="9">
         <v>45279</v>
       </c>
       <c r="B69" t="s">
@@ -2455,8 +1856,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="8">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70" s="9">
         <v>45280</v>
       </c>
       <c r="B70" t="s">
@@ -2472,8 +1873,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="8">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71" s="9">
         <v>45281</v>
       </c>
       <c r="B71" t="s">
@@ -2489,8 +1890,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="8">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72" s="9">
         <v>45282</v>
       </c>
       <c r="B72" t="s">
@@ -2506,8 +1907,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="8">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73" s="9">
         <v>45283</v>
       </c>
       <c r="B73" t="s">
@@ -2523,8 +1924,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="8">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74" s="9">
         <v>45284</v>
       </c>
       <c r="B74" t="s">
@@ -2540,8 +1941,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="8">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75" s="9">
         <v>45285</v>
       </c>
       <c r="B75" t="s">
@@ -2557,8 +1958,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="8">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76" s="9">
         <v>45286</v>
       </c>
       <c r="B76" t="s">
@@ -2574,8 +1975,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="8">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="9">
         <v>45287</v>
       </c>
       <c r="B77" t="s">
@@ -2591,8 +1992,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="8">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="9">
         <v>45288</v>
       </c>
       <c r="B78" t="s">
@@ -2608,8 +2009,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="8">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="9">
         <v>45289</v>
       </c>
       <c r="B79" t="s">
@@ -2625,8 +2026,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="8">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="9">
         <v>45290</v>
       </c>
       <c r="B80" t="s">
@@ -2642,8 +2043,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="8">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A81" s="9">
         <v>45291</v>
       </c>
       <c r="B81" t="s">
@@ -2659,8 +2060,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="8">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A82" s="9">
         <v>45292</v>
       </c>
       <c r="B82" t="s">
@@ -2676,8 +2077,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="8">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A83" s="9">
         <v>45293</v>
       </c>
       <c r="B83" t="s">
@@ -2693,8 +2094,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="8">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A84" s="9">
         <v>45294</v>
       </c>
       <c r="B84" t="s">
@@ -2713,8 +2114,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="8">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A85" s="9">
         <v>45295</v>
       </c>
       <c r="B85" t="s">
@@ -2730,8 +2131,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="8">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A86" s="9">
         <v>45296</v>
       </c>
       <c r="B86" t="s">
@@ -2747,8 +2148,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="8">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A87" s="9">
         <v>45297</v>
       </c>
       <c r="B87" t="s">
@@ -2764,8 +2165,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="8">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A88" s="9">
         <v>45298</v>
       </c>
       <c r="B88" t="s">
@@ -2781,8 +2182,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="8">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A89" s="9">
         <v>45299</v>
       </c>
       <c r="B89" t="s">
@@ -2798,8 +2199,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="8">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A90" s="9">
         <v>45300</v>
       </c>
       <c r="B90" t="s">
@@ -2815,8 +2216,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="8">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A91" s="9">
         <v>45301</v>
       </c>
       <c r="B91" t="s">
@@ -2832,8 +2233,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="8">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A92" s="9">
         <v>45302</v>
       </c>
       <c r="B92" t="s">
@@ -2849,8 +2250,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="8">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A93" s="9">
         <v>45303</v>
       </c>
       <c r="B93" t="s">
@@ -2866,8 +2267,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="8">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A94" s="9">
         <v>45304</v>
       </c>
       <c r="B94" t="s">
@@ -2883,8 +2284,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="8">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A95" s="9">
         <v>45305</v>
       </c>
       <c r="B95" t="s">
@@ -2903,8 +2304,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="8">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A96" s="9">
         <v>45306</v>
       </c>
       <c r="B96" t="s">
@@ -2920,8 +2321,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="8">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A97" s="9">
         <v>45307</v>
       </c>
       <c r="B97" t="s">
@@ -2937,8 +2338,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="8">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A98" s="9">
         <v>45308</v>
       </c>
       <c r="B98" t="s">
@@ -2954,8 +2355,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="8">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A99" s="9">
         <v>45309</v>
       </c>
       <c r="B99" t="s">
@@ -2971,8 +2372,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="8">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A100" s="9">
         <v>45310</v>
       </c>
       <c r="B100" t="s">
@@ -2988,8 +2389,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="8">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A101" s="9">
         <v>45311</v>
       </c>
       <c r="B101" t="s">
@@ -3005,8 +2406,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="8">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A102" s="9">
         <v>45312</v>
       </c>
       <c r="B102" t="s">
@@ -3022,8 +2423,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="8">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A103" s="9">
         <v>45313</v>
       </c>
       <c r="B103" t="s">
@@ -3039,8 +2440,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="8">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A104" s="9">
         <v>45314</v>
       </c>
       <c r="B104" t="s">
@@ -3056,8 +2457,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="8">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A105" s="9">
         <v>45315</v>
       </c>
       <c r="B105" t="s">
@@ -3073,8 +2474,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="8">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A106" s="9">
         <v>45316</v>
       </c>
       <c r="B106" t="s">
@@ -3090,8 +2491,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="8">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A107" s="9">
         <v>45317</v>
       </c>
       <c r="B107" t="s">
@@ -3107,8 +2508,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="8">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A108" s="9">
         <v>45318</v>
       </c>
       <c r="B108" t="s">
@@ -3124,8 +2525,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="8">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A109" s="9">
         <v>45319</v>
       </c>
       <c r="B109" t="s">
@@ -3141,8 +2542,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="8">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A110" s="9">
         <v>45320</v>
       </c>
       <c r="B110" t="s">
@@ -3158,8 +2559,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="8">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A111" s="9">
         <v>45321</v>
       </c>
       <c r="B111" t="s">
@@ -3175,8 +2576,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="8">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A112" s="9">
         <v>45322</v>
       </c>
       <c r="B112" t="s">
@@ -3192,8 +2593,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="8">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A113" s="9">
         <v>45323</v>
       </c>
       <c r="B113" t="s">
@@ -3209,8 +2610,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="8">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A114" s="9">
         <v>45324</v>
       </c>
       <c r="B114" t="s">
@@ -3226,8 +2627,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="8">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A115" s="9">
         <v>45325</v>
       </c>
       <c r="B115" t="s">
@@ -3243,8 +2644,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="8">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A116" s="9">
         <v>45326</v>
       </c>
       <c r="B116" t="s">
@@ -3260,8 +2661,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="8">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A117" s="9">
         <v>45327</v>
       </c>
       <c r="B117" t="s">
@@ -3277,8 +2678,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="8">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A118" s="9">
         <v>45328</v>
       </c>
       <c r="B118" t="s">
@@ -3294,8 +2695,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="8">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A119" s="9">
         <v>45329</v>
       </c>
       <c r="B119" t="s">
@@ -3311,8 +2712,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="8">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A120" s="9">
         <v>45330</v>
       </c>
       <c r="B120" t="s">
@@ -3328,8 +2729,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
-      <c r="A121" s="8">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A121" s="9">
         <v>45331</v>
       </c>
       <c r="B121" t="s">
@@ -3348,8 +2749,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="8">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A122" s="9">
         <v>45332</v>
       </c>
       <c r="B122" t="s">
@@ -3365,8 +2766,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="8">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A123" s="9">
         <v>45333</v>
       </c>
       <c r="B123" t="s">
@@ -3382,8 +2783,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="8">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A124" s="9">
         <v>45334</v>
       </c>
       <c r="B124" t="s">
@@ -3399,8 +2800,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="8">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A125" s="9">
         <v>45335</v>
       </c>
       <c r="B125" t="s">
@@ -3416,8 +2817,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="8">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A126" s="9">
         <v>45336</v>
       </c>
       <c r="B126" t="s">
@@ -3433,8 +2834,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="8">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A127" s="9">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
@@ -3450,8 +2851,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="8">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A128" s="9">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
@@ -3467,8 +2868,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="8">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A129" s="9">
         <v>45339</v>
       </c>
       <c r="B129" t="s">
@@ -3484,8 +2885,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="8">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A130" s="9">
         <v>45340</v>
       </c>
       <c r="B130" t="s">
@@ -3501,8 +2902,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="8">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A131" s="9">
         <v>45341</v>
       </c>
       <c r="B131" t="s">
@@ -3518,8 +2919,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="8">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A132" s="9">
         <v>45342</v>
       </c>
       <c r="B132" t="s">
@@ -3535,8 +2936,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="8">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A133" s="9">
         <v>45343</v>
       </c>
       <c r="B133" t="s">
@@ -3552,8 +2953,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="8">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A134" s="9">
         <v>45344</v>
       </c>
       <c r="B134" t="s">
@@ -3569,8 +2970,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="8">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A135" s="9">
         <v>45345</v>
       </c>
       <c r="B135" t="s">
@@ -3586,8 +2987,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="8">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A136" s="9">
         <v>45346</v>
       </c>
       <c r="B136" t="s">
@@ -3603,8 +3004,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="8">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A137" s="9">
         <v>45347</v>
       </c>
       <c r="B137" t="s">
@@ -3620,8 +3021,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="8">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A138" s="9">
         <v>45348</v>
       </c>
       <c r="B138" t="s">
@@ -3637,11 +3038,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="8">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A139" s="9">
         <v>45349</v>
       </c>
-      <c r="B139"/>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>6</v>
+      </c>
       <c r="D139" t="s">
         <v>8</v>
       </c>
@@ -3649,10 +3055,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
-      <c r="A140" s="8">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A140" s="9">
         <v>45350</v>
       </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>6</v>
+      </c>
       <c r="D140" t="s">
         <v>8</v>
       </c>
@@ -3660,8 +3072,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="8">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A141" s="9">
         <v>45351</v>
       </c>
       <c r="B141" t="s">
@@ -3677,8 +3089,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="8">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A142" s="9">
         <v>45352</v>
       </c>
       <c r="D142" t="s">
@@ -3688,8 +3100,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="8">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A143" s="9">
         <v>45353</v>
       </c>
       <c r="B143" t="s">
@@ -3698,9 +3110,15 @@
       <c r="C143" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
-      <c r="A144" s="8">
+      <c r="D143" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A144" s="9">
         <v>45354</v>
       </c>
       <c r="B144" t="s">
@@ -3710,41 +3128,43 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="8">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A145" s="9">
         <v>45355</v>
       </c>
     </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="8">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A146" s="9">
         <v>45356</v>
       </c>
     </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="8">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A147" s="9">
         <v>45357</v>
       </c>
     </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="8">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A148" s="9">
         <v>45358</v>
       </c>
     </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A149" s="9">
+        <v>45359</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F148">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:F148" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -3753,7 +3173,7 @@
     <col min="5" max="5" width="21.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
@@ -3770,7 +3190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
@@ -3787,7 +3207,7 @@
         <v>45260</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3801,10 +3221,10 @@
         <v>24</v>
       </c>
       <c r="E3" s="4">
-        <v>45318.4237731481</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>45318.423773148097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -3818,10 +3238,10 @@
         <v>24</v>
       </c>
       <c r="E4" s="4">
-        <v>45318.4237731481</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>45318.423773148097</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3835,10 +3255,10 @@
         <v>24</v>
       </c>
       <c r="E5" s="4">
-        <v>45318.4237731481</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>45318.423773148097</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3852,10 +3272,10 @@
         <v>24</v>
       </c>
       <c r="E6" s="4">
-        <v>45318.4237731481</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>45318.423773148097</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3869,29 +3289,26 @@
         <v>34</v>
       </c>
       <c r="E7" s="4">
-        <v>45328.6316550926</v>
+        <v>45328.631655092599</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E7">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:E7" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -3899,7 +3316,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3907,7 +3324,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -3915,7 +3332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -3923,7 +3340,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -3931,7 +3348,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -3939,7 +3356,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -3947,7 +3364,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -3955,7 +3372,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -3963,7 +3380,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -3971,7 +3388,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -3979,7 +3396,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -3987,7 +3404,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -3995,7 +3412,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -4003,7 +3420,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -4011,7 +3428,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -4019,7 +3436,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -4027,7 +3444,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -4035,7 +3452,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -4043,7 +3460,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -4051,7 +3468,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>62</v>
       </c>
@@ -4059,7 +3476,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4067,7 +3484,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -4075,7 +3492,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -4083,7 +3500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -4091,7 +3508,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -4099,7 +3516,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -4107,7 +3524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -4116,163 +3533,158 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B28">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:B28" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>100006</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>100033</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>100556</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>105470</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>153240</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>101398</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>84</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -1271,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -2848,6 +2848,31 @@
     <row r="148" spans="1:1">
       <c r="A148" s="9">
         <v>45358</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="9">
+        <v>45359</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="9">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="9">
+        <v>45361</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="9">
+        <v>45362</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="9">
+        <v>45363</v>
       </c>
     </row>
   </sheetData>
@@ -3028,16 +3053,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4">
-        <v>45349</v>
+        <v>45352</v>
       </c>
       <c r="B2" s="4">
-        <v>45358</v>
+        <v>45359</v>
       </c>
       <c r="C2" s="4">
-        <v>45355</v>
+        <v>45356</v>
       </c>
       <c r="D2" s="4">
-        <v>45355</v>
+        <v>45356</v>
       </c>
     </row>
   </sheetData>

--- a/data/Config.xlsx
+++ b/data/Config.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\SourceCode\Work-Chinapost\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA624A73-8685-407B-B0CC-65E5E0DAE02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="排产状况表" sheetId="5" r:id="rId1"/>
@@ -21,9 +15,9 @@
     <sheet name="分装工位表" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产状况表!$A$1:$F$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">库区表!$A$1:$B$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">临时不出库物料表!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排产状况表!$A$1:$F$148</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="87">
   <si>
     <t>生产日期</t>
   </si>
@@ -146,6 +142,12 @@
   </si>
   <si>
     <t>走橡塑拉动</t>
+  </si>
+  <si>
+    <t>AZ900036000012</t>
+  </si>
+  <si>
+    <t>调拨</t>
   </si>
   <si>
     <t>库区编码</t>
@@ -301,12 +303,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[$-409]yyyy/mm/dd\ hh:mm\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,7 +324,6 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -327,35 +332,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -363,12 +682,254 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -393,25 +954,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -661,24 +1266,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F149"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="9" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="8" customWidth="1"/>
     <col min="2" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="5" width="7.375" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
     <col min="8" max="8" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -697,8 +1302,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="9">
+    <row r="2" spans="1:5">
+      <c r="A2" s="8">
         <v>45212</v>
       </c>
       <c r="B2" t="s">
@@ -714,8 +1319,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="9">
+    <row r="3" spans="1:5">
+      <c r="A3" s="8">
         <v>45213</v>
       </c>
       <c r="B3" t="s">
@@ -731,8 +1336,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="9">
+    <row r="4" spans="1:5">
+      <c r="A4" s="8">
         <v>45214</v>
       </c>
       <c r="B4" t="s">
@@ -748,8 +1353,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="9">
+    <row r="5" spans="1:5">
+      <c r="A5" s="8">
         <v>45215</v>
       </c>
       <c r="B5" t="s">
@@ -765,8 +1370,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="9">
+    <row r="6" spans="1:5">
+      <c r="A6" s="8">
         <v>45216</v>
       </c>
       <c r="B6" t="s">
@@ -782,8 +1387,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="9">
+    <row r="7" spans="1:5">
+      <c r="A7" s="8">
         <v>45217</v>
       </c>
       <c r="B7" t="s">
@@ -799,8 +1404,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="9">
+    <row r="8" spans="1:5">
+      <c r="A8" s="8">
         <v>45218</v>
       </c>
       <c r="B8" t="s">
@@ -816,8 +1421,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="9">
+    <row r="9" spans="1:5">
+      <c r="A9" s="8">
         <v>45219</v>
       </c>
       <c r="B9" t="s">
@@ -833,8 +1438,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="9">
+    <row r="10" spans="1:5">
+      <c r="A10" s="8">
         <v>45220</v>
       </c>
       <c r="B10" t="s">
@@ -850,8 +1455,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A11" s="9">
+    <row r="11" spans="1:5">
+      <c r="A11" s="8">
         <v>45221</v>
       </c>
       <c r="B11" t="s">
@@ -867,8 +1472,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="9">
+    <row r="12" spans="1:5">
+      <c r="A12" s="8">
         <v>45222</v>
       </c>
       <c r="B12" t="s">
@@ -884,8 +1489,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="9">
+    <row r="13" spans="1:5">
+      <c r="A13" s="8">
         <v>45223</v>
       </c>
       <c r="B13" t="s">
@@ -901,8 +1506,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A14" s="9">
+    <row r="14" spans="1:5">
+      <c r="A14" s="8">
         <v>45224</v>
       </c>
       <c r="B14" t="s">
@@ -918,8 +1523,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="9">
+    <row r="15" spans="1:5">
+      <c r="A15" s="8">
         <v>45225</v>
       </c>
       <c r="B15" t="s">
@@ -935,8 +1540,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A16" s="9">
+    <row r="16" spans="1:5">
+      <c r="A16" s="8">
         <v>45226</v>
       </c>
       <c r="B16" t="s">
@@ -952,8 +1557,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="9">
+    <row r="17" spans="1:5">
+      <c r="A17" s="8">
         <v>45227</v>
       </c>
       <c r="B17" t="s">
@@ -969,8 +1574,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="9">
+    <row r="18" spans="1:5">
+      <c r="A18" s="8">
         <v>45228</v>
       </c>
       <c r="B18" t="s">
@@ -986,8 +1591,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="9">
+    <row r="19" spans="1:5">
+      <c r="A19" s="8">
         <v>45229</v>
       </c>
       <c r="B19" t="s">
@@ -1003,8 +1608,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="9">
+    <row r="20" spans="1:5">
+      <c r="A20" s="8">
         <v>45230</v>
       </c>
       <c r="B20" t="s">
@@ -1020,8 +1625,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="9">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8">
         <v>45231</v>
       </c>
       <c r="B21" t="s">
@@ -1037,8 +1642,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="9">
+    <row r="22" spans="1:5">
+      <c r="A22" s="8">
         <v>45232</v>
       </c>
       <c r="B22" t="s">
@@ -1054,8 +1659,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="9">
+    <row r="23" spans="1:5">
+      <c r="A23" s="8">
         <v>45233</v>
       </c>
       <c r="B23" t="s">
@@ -1071,8 +1676,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="9">
+    <row r="24" spans="1:5">
+      <c r="A24" s="8">
         <v>45234</v>
       </c>
       <c r="B24" t="s">
@@ -1088,8 +1693,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="9">
+    <row r="25" spans="1:5">
+      <c r="A25" s="8">
         <v>45235</v>
       </c>
       <c r="B25" t="s">
@@ -1105,8 +1710,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="9">
+    <row r="26" spans="1:5">
+      <c r="A26" s="8">
         <v>45236</v>
       </c>
       <c r="B26" t="s">
@@ -1122,8 +1727,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="9">
+    <row r="27" spans="1:5">
+      <c r="A27" s="8">
         <v>45237</v>
       </c>
       <c r="B27" t="s">
@@ -1139,8 +1744,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="9">
+    <row r="28" spans="1:5">
+      <c r="A28" s="8">
         <v>45238</v>
       </c>
       <c r="B28" t="s">
@@ -1156,8 +1761,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="9">
+    <row r="29" spans="1:5">
+      <c r="A29" s="8">
         <v>45239</v>
       </c>
       <c r="B29" t="s">
@@ -1173,8 +1778,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="9">
+    <row r="30" spans="1:5">
+      <c r="A30" s="8">
         <v>45240</v>
       </c>
       <c r="B30" t="s">
@@ -1190,8 +1795,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="9">
+    <row r="31" spans="1:5">
+      <c r="A31" s="8">
         <v>45241</v>
       </c>
       <c r="B31" t="s">
@@ -1207,8 +1812,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="9">
+    <row r="32" spans="1:5">
+      <c r="A32" s="8">
         <v>45242</v>
       </c>
       <c r="B32" t="s">
@@ -1224,8 +1829,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="9">
+    <row r="33" spans="1:5">
+      <c r="A33" s="8">
         <v>45243</v>
       </c>
       <c r="B33" t="s">
@@ -1241,8 +1846,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="9">
+    <row r="34" spans="1:5">
+      <c r="A34" s="8">
         <v>45244</v>
       </c>
       <c r="B34" t="s">
@@ -1258,8 +1863,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="9">
+    <row r="35" spans="1:5">
+      <c r="A35" s="8">
         <v>45245</v>
       </c>
       <c r="B35" t="s">
@@ -1275,8 +1880,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="9">
+    <row r="36" spans="1:5">
+      <c r="A36" s="8">
         <v>45246</v>
       </c>
       <c r="B36" t="s">
@@ -1292,8 +1897,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="9">
+    <row r="37" spans="1:5">
+      <c r="A37" s="8">
         <v>45247</v>
       </c>
       <c r="B37" t="s">
@@ -1309,8 +1914,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="9">
+    <row r="38" spans="1:5">
+      <c r="A38" s="8">
         <v>45248</v>
       </c>
       <c r="B38" t="s">
@@ -1326,8 +1931,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="9">
+    <row r="39" spans="1:5">
+      <c r="A39" s="8">
         <v>45249</v>
       </c>
       <c r="B39" t="s">
@@ -1343,8 +1948,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="9">
+    <row r="40" spans="1:5">
+      <c r="A40" s="8">
         <v>45250</v>
       </c>
       <c r="B40" t="s">
@@ -1360,8 +1965,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="9">
+    <row r="41" spans="1:5">
+      <c r="A41" s="8">
         <v>45251</v>
       </c>
       <c r="B41" t="s">
@@ -1377,8 +1982,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="9">
+    <row r="42" spans="1:5">
+      <c r="A42" s="8">
         <v>45252</v>
       </c>
       <c r="B42" t="s">
@@ -1394,8 +1999,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="9">
+    <row r="43" spans="1:5">
+      <c r="A43" s="8">
         <v>45253</v>
       </c>
       <c r="B43" t="s">
@@ -1411,8 +2016,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="9">
+    <row r="44" spans="1:5">
+      <c r="A44" s="8">
         <v>45254</v>
       </c>
       <c r="B44" t="s">
@@ -1428,8 +2033,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="9">
+    <row r="45" spans="1:5">
+      <c r="A45" s="8">
         <v>45255</v>
       </c>
       <c r="B45" t="s">
@@ -1445,8 +2050,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="9">
+    <row r="46" spans="1:5">
+      <c r="A46" s="8">
         <v>45256</v>
       </c>
       <c r="B46" t="s">
@@ -1462,8 +2067,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="9">
+    <row r="47" spans="1:5">
+      <c r="A47" s="8">
         <v>45257</v>
       </c>
       <c r="B47" t="s">
@@ -1479,8 +2084,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="9">
+    <row r="48" spans="1:5">
+      <c r="A48" s="8">
         <v>45258</v>
       </c>
       <c r="B48" t="s">
@@ -1496,8 +2101,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A49" s="9">
+    <row r="49" spans="1:5">
+      <c r="A49" s="8">
         <v>45259</v>
       </c>
       <c r="B49" t="s">
@@ -1513,8 +2118,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A50" s="9">
+    <row r="50" spans="1:5">
+      <c r="A50" s="8">
         <v>45260</v>
       </c>
       <c r="B50" t="s">
@@ -1530,8 +2135,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A51" s="9">
+    <row r="51" spans="1:5">
+      <c r="A51" s="8">
         <v>45261</v>
       </c>
       <c r="B51" t="s">
@@ -1547,8 +2152,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A52" s="9">
+    <row r="52" spans="1:5">
+      <c r="A52" s="8">
         <v>45262</v>
       </c>
       <c r="B52" t="s">
@@ -1564,8 +2169,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A53" s="9">
+    <row r="53" spans="1:5">
+      <c r="A53" s="8">
         <v>45263</v>
       </c>
       <c r="B53" t="s">
@@ -1581,8 +2186,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A54" s="9">
+    <row r="54" spans="1:5">
+      <c r="A54" s="8">
         <v>45264</v>
       </c>
       <c r="B54" t="s">
@@ -1598,8 +2203,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A55" s="9">
+    <row r="55" spans="1:5">
+      <c r="A55" s="8">
         <v>45265</v>
       </c>
       <c r="B55" t="s">
@@ -1615,8 +2220,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A56" s="9">
+    <row r="56" spans="1:5">
+      <c r="A56" s="8">
         <v>45266</v>
       </c>
       <c r="B56" t="s">
@@ -1632,8 +2237,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A57" s="9">
+    <row r="57" spans="1:5">
+      <c r="A57" s="8">
         <v>45267</v>
       </c>
       <c r="B57" t="s">
@@ -1649,8 +2254,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A58" s="9">
+    <row r="58" spans="1:5">
+      <c r="A58" s="8">
         <v>45268</v>
       </c>
       <c r="B58" t="s">
@@ -1666,8 +2271,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A59" s="9">
+    <row r="59" spans="1:5">
+      <c r="A59" s="8">
         <v>45269</v>
       </c>
       <c r="B59" t="s">
@@ -1683,8 +2288,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A60" s="9">
+    <row r="60" spans="1:6">
+      <c r="A60" s="8">
         <v>45270</v>
       </c>
       <c r="B60" t="s">
@@ -1703,8 +2308,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A61" s="9">
+    <row r="61" spans="1:5">
+      <c r="A61" s="8">
         <v>45271</v>
       </c>
       <c r="B61" t="s">
@@ -1720,8 +2325,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A62" s="9">
+    <row r="62" spans="1:5">
+      <c r="A62" s="8">
         <v>45272</v>
       </c>
       <c r="B62" t="s">
@@ -1737,8 +2342,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A63" s="9">
+    <row r="63" spans="1:5">
+      <c r="A63" s="8">
         <v>45273</v>
       </c>
       <c r="B63" t="s">
@@ -1754,8 +2359,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A64" s="9">
+    <row r="64" spans="1:5">
+      <c r="A64" s="8">
         <v>45274</v>
       </c>
       <c r="B64" t="s">
@@ -1771,8 +2376,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="9">
+    <row r="65" spans="1:5">
+      <c r="A65" s="8">
         <v>45275</v>
       </c>
       <c r="B65" t="s">
@@ -1788,8 +2393,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="9">
+    <row r="66" spans="1:5">
+      <c r="A66" s="8">
         <v>45276</v>
       </c>
       <c r="B66" t="s">
@@ -1805,8 +2410,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="9">
+    <row r="67" spans="1:5">
+      <c r="A67" s="8">
         <v>45277</v>
       </c>
       <c r="B67" t="s">
@@ -1822,8 +2427,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="9">
+    <row r="68" spans="1:5">
+      <c r="A68" s="8">
         <v>45278</v>
       </c>
       <c r="B68" t="s">
@@ -1839,8 +2444,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="9">
+    <row r="69" spans="1:5">
+      <c r="A69" s="8">
         <v>45279</v>
       </c>
       <c r="B69" t="s">
@@ -1856,8 +2461,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="9">
+    <row r="70" spans="1:5">
+      <c r="A70" s="8">
         <v>45280</v>
       </c>
       <c r="B70" t="s">
@@ -1873,8 +2478,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="9">
+    <row r="71" spans="1:5">
+      <c r="A71" s="8">
         <v>45281</v>
       </c>
       <c r="B71" t="s">
@@ -1890,8 +2495,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="9">
+    <row r="72" spans="1:5">
+      <c r="A72" s="8">
         <v>45282</v>
       </c>
       <c r="B72" t="s">
@@ -1907,8 +2512,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A73" s="9">
+    <row r="73" spans="1:5">
+      <c r="A73" s="8">
         <v>45283</v>
       </c>
       <c r="B73" t="s">
@@ -1924,8 +2529,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A74" s="9">
+    <row r="74" spans="1:5">
+      <c r="A74" s="8">
         <v>45284</v>
       </c>
       <c r="B74" t="s">
@@ -1941,8 +2546,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A75" s="9">
+    <row r="75" spans="1:5">
+      <c r="A75" s="8">
         <v>45285</v>
       </c>
       <c r="B75" t="s">
@@ -1958,8 +2563,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A76" s="9">
+    <row r="76" spans="1:5">
+      <c r="A76" s="8">
         <v>45286</v>
       </c>
       <c r="B76" t="s">
@@ -1975,8 +2580,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A77" s="9">
+    <row r="77" spans="1:5">
+      <c r="A77" s="8">
         <v>45287</v>
       </c>
       <c r="B77" t="s">
@@ -1992,8 +2597,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="9">
+    <row r="78" spans="1:5">
+      <c r="A78" s="8">
         <v>45288</v>
       </c>
       <c r="B78" t="s">
@@ -2009,8 +2614,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="9">
+    <row r="79" spans="1:5">
+      <c r="A79" s="8">
         <v>45289</v>
       </c>
       <c r="B79" t="s">
@@ -2026,8 +2631,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="9">
+    <row r="80" spans="1:5">
+      <c r="A80" s="8">
         <v>45290</v>
       </c>
       <c r="B80" t="s">
@@ -2043,8 +2648,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A81" s="9">
+    <row r="81" spans="1:5">
+      <c r="A81" s="8">
         <v>45291</v>
       </c>
       <c r="B81" t="s">
@@ -2060,8 +2665,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A82" s="9">
+    <row r="82" spans="1:5">
+      <c r="A82" s="8">
         <v>45292</v>
       </c>
       <c r="B82" t="s">
@@ -2077,8 +2682,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A83" s="9">
+    <row r="83" spans="1:5">
+      <c r="A83" s="8">
         <v>45293</v>
       </c>
       <c r="B83" t="s">
@@ -2094,8 +2699,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A84" s="9">
+    <row r="84" spans="1:6">
+      <c r="A84" s="8">
         <v>45294</v>
       </c>
       <c r="B84" t="s">
@@ -2114,8 +2719,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A85" s="9">
+    <row r="85" spans="1:5">
+      <c r="A85" s="8">
         <v>45295</v>
       </c>
       <c r="B85" t="s">
@@ -2131,8 +2736,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A86" s="9">
+    <row r="86" spans="1:5">
+      <c r="A86" s="8">
         <v>45296</v>
       </c>
       <c r="B86" t="s">
@@ -2148,8 +2753,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A87" s="9">
+    <row r="87" spans="1:5">
+      <c r="A87" s="8">
         <v>45297</v>
       </c>
       <c r="B87" t="s">
@@ -2165,8 +2770,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A88" s="9">
+    <row r="88" spans="1:5">
+      <c r="A88" s="8">
         <v>45298</v>
       </c>
       <c r="B88" t="s">
@@ -2182,8 +2787,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A89" s="9">
+    <row r="89" spans="1:5">
+      <c r="A89" s="8">
         <v>45299</v>
       </c>
       <c r="B89" t="s">
@@ -2199,8 +2804,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A90" s="9">
+    <row r="90" spans="1:5">
+      <c r="A90" s="8">
         <v>45300</v>
       </c>
       <c r="B90" t="s">
@@ -2216,8 +2821,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A91" s="9">
+    <row r="91" spans="1:5">
+      <c r="A91" s="8">
         <v>45301</v>
       </c>
       <c r="B91" t="s">
@@ -2233,8 +2838,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A92" s="9">
+    <row r="92" spans="1:5">
+      <c r="A92" s="8">
         <v>45302</v>
       </c>
       <c r="B92" t="s">
@@ -2250,8 +2855,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A93" s="9">
+    <row r="93" spans="1:5">
+      <c r="A93" s="8">
         <v>45303</v>
       </c>
       <c r="B93" t="s">
@@ -2267,8 +2872,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A94" s="9">
+    <row r="94" spans="1:5">
+      <c r="A94" s="8">
         <v>45304</v>
       </c>
       <c r="B94" t="s">
@@ -2284,8 +2889,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A95" s="9">
+    <row r="95" spans="1:6">
+      <c r="A95" s="8">
         <v>45305</v>
       </c>
       <c r="B95" t="s">
@@ -2304,8 +2909,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A96" s="9">
+    <row r="96" spans="1:5">
+      <c r="A96" s="8">
         <v>45306</v>
       </c>
       <c r="B96" t="s">
@@ -2321,8 +2926,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97" s="9">
+    <row r="97" spans="1:5">
+      <c r="A97" s="8">
         <v>45307</v>
       </c>
       <c r="B97" t="s">
@@ -2338,8 +2943,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A98" s="9">
+    <row r="98" spans="1:5">
+      <c r="A98" s="8">
         <v>45308</v>
       </c>
       <c r="B98" t="s">
@@ -2355,8 +2960,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A99" s="9">
+    <row r="99" spans="1:5">
+      <c r="A99" s="8">
         <v>45309</v>
       </c>
       <c r="B99" t="s">
@@ -2372,8 +2977,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A100" s="9">
+    <row r="100" spans="1:5">
+      <c r="A100" s="8">
         <v>45310</v>
       </c>
       <c r="B100" t="s">
@@ -2389,8 +2994,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A101" s="9">
+    <row r="101" spans="1:5">
+      <c r="A101" s="8">
         <v>45311</v>
       </c>
       <c r="B101" t="s">
@@ -2406,8 +3011,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A102" s="9">
+    <row r="102" spans="1:5">
+      <c r="A102" s="8">
         <v>45312</v>
       </c>
       <c r="B102" t="s">
@@ -2423,8 +3028,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A103" s="9">
+    <row r="103" spans="1:5">
+      <c r="A103" s="8">
         <v>45313</v>
       </c>
       <c r="B103" t="s">
@@ -2440,8 +3045,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A104" s="9">
+    <row r="104" spans="1:5">
+      <c r="A104" s="8">
         <v>45314</v>
       </c>
       <c r="B104" t="s">
@@ -2457,8 +3062,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A105" s="9">
+    <row r="105" spans="1:5">
+      <c r="A105" s="8">
         <v>45315</v>
       </c>
       <c r="B105" t="s">
@@ -2474,8 +3079,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A106" s="9">
+    <row r="106" spans="1:5">
+      <c r="A106" s="8">
         <v>45316</v>
       </c>
       <c r="B106" t="s">
@@ -2491,8 +3096,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A107" s="9">
+    <row r="107" spans="1:5">
+      <c r="A107" s="8">
         <v>45317</v>
       </c>
       <c r="B107" t="s">
@@ -2508,8 +3113,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A108" s="9">
+    <row r="108" spans="1:5">
+      <c r="A108" s="8">
         <v>45318</v>
       </c>
       <c r="B108" t="s">
@@ -2525,8 +3130,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A109" s="9">
+    <row r="109" spans="1:5">
+      <c r="A109" s="8">
         <v>45319</v>
       </c>
       <c r="B109" t="s">
@@ -2542,8 +3147,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A110" s="9">
+    <row r="110" spans="1:5">
+      <c r="A110" s="8">
         <v>45320</v>
       </c>
       <c r="B110" t="s">
@@ -2559,8 +3164,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A111" s="9">
+    <row r="111" spans="1:5">
+      <c r="A111" s="8">
         <v>45321</v>
       </c>
       <c r="B111" t="s">
@@ -2576,8 +3181,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A112" s="9">
+    <row r="112" spans="1:5">
+      <c r="A112" s="8">
         <v>45322</v>
       </c>
       <c r="B112" t="s">
@@ -2593,8 +3198,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A113" s="9">
+    <row r="113" spans="1:5">
+      <c r="A113" s="8">
         <v>45323</v>
       </c>
       <c r="B113" t="s">
@@ -2610,8 +3215,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A114" s="9">
+    <row r="114" spans="1:5">
+      <c r="A114" s="8">
         <v>45324</v>
       </c>
       <c r="B114" t="s">
@@ -2627,8 +3232,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A115" s="9">
+    <row r="115" spans="1:5">
+      <c r="A115" s="8">
         <v>45325</v>
       </c>
       <c r="B115" t="s">
@@ -2644,8 +3249,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A116" s="9">
+    <row r="116" spans="1:5">
+      <c r="A116" s="8">
         <v>45326</v>
       </c>
       <c r="B116" t="s">
@@ -2661,8 +3266,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A117" s="9">
+    <row r="117" spans="1:5">
+      <c r="A117" s="8">
         <v>45327</v>
       </c>
       <c r="B117" t="s">
@@ -2678,8 +3283,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A118" s="9">
+    <row r="118" spans="1:5">
+      <c r="A118" s="8">
         <v>45328</v>
       </c>
       <c r="B118" t="s">
@@ -2695,8 +3300,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A119" s="9">
+    <row r="119" spans="1:5">
+      <c r="A119" s="8">
         <v>45329</v>
       </c>
       <c r="B119" t="s">
@@ -2712,8 +3317,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A120" s="9">
+    <row r="120" spans="1:5">
+      <c r="A120" s="8">
         <v>45330</v>
       </c>
       <c r="B120" t="s">
@@ -2729,8 +3334,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A121" s="9">
+    <row r="121" spans="1:6">
+      <c r="A121" s="8">
         <v>45331</v>
       </c>
       <c r="B121" t="s">
@@ -2749,8 +3354,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A122" s="9">
+    <row r="122" spans="1:5">
+      <c r="A122" s="8">
         <v>45332</v>
       </c>
       <c r="B122" t="s">
@@ -2766,8 +3371,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A123" s="9">
+    <row r="123" spans="1:5">
+      <c r="A123" s="8">
         <v>45333</v>
       </c>
       <c r="B123" t="s">
@@ -2783,8 +3388,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A124" s="9">
+    <row r="124" spans="1:5">
+      <c r="A124" s="8">
         <v>45334</v>
       </c>
       <c r="B124" t="s">
@@ -2800,8 +3405,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A125" s="9">
+    <row r="125" spans="1:5">
+      <c r="A125" s="8">
         <v>45335</v>
       </c>
       <c r="B125" t="s">
@@ -2817,8 +3422,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A126" s="9">
+    <row r="126" spans="1:5">
+      <c r="A126" s="8">
         <v>45336</v>
       </c>
       <c r="B126" t="s">
@@ -2834,8 +3439,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A127" s="9">
+    <row r="127" spans="1:5">
+      <c r="A127" s="8">
         <v>45337</v>
       </c>
       <c r="B127" t="s">
@@ -2851,8 +3456,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A128" s="9">
+    <row r="128" spans="1:5">
+      <c r="A128" s="8">
         <v>45338</v>
       </c>
       <c r="B128" t="s">
@@ -2868,8 +3473,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A129" s="9">
+    <row r="129" spans="1:5">
+      <c r="A129" s="8">
         <v>45339</v>
       </c>
       <c r="B129" t="s">
@@ -2885,8 +3490,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A130" s="9">
+    <row r="130" spans="1:5">
+      <c r="A130" s="8">
         <v>45340</v>
       </c>
       <c r="B130" t="s">
@@ -2902,8 +3507,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A131" s="9">
+    <row r="131" spans="1:5">
+      <c r="A131" s="8">
         <v>45341</v>
       </c>
       <c r="B131" t="s">
@@ -2919,8 +3524,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A132" s="9">
+    <row r="132" spans="1:5">
+      <c r="A132" s="8">
         <v>45342</v>
       </c>
       <c r="B132" t="s">
@@ -2936,8 +3541,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A133" s="9">
+    <row r="133" spans="1:5">
+      <c r="A133" s="8">
         <v>45343</v>
       </c>
       <c r="B133" t="s">
@@ -2953,8 +3558,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A134" s="9">
+    <row r="134" spans="1:5">
+      <c r="A134" s="8">
         <v>45344</v>
       </c>
       <c r="B134" t="s">
@@ -2970,8 +3575,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A135" s="9">
+    <row r="135" spans="1:5">
+      <c r="A135" s="8">
         <v>45345</v>
       </c>
       <c r="B135" t="s">
@@ -2987,8 +3592,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A136" s="9">
+    <row r="136" spans="1:5">
+      <c r="A136" s="8">
         <v>45346</v>
       </c>
       <c r="B136" t="s">
@@ -3004,8 +3609,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A137" s="9">
+    <row r="137" spans="1:5">
+      <c r="A137" s="8">
         <v>45347</v>
       </c>
       <c r="B137" t="s">
@@ -3021,8 +3626,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A138" s="9">
+    <row r="138" spans="1:5">
+      <c r="A138" s="8">
         <v>45348</v>
       </c>
       <c r="B138" t="s">
@@ -3038,8 +3643,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A139" s="9">
+    <row r="139" spans="1:5">
+      <c r="A139" s="8">
         <v>45349</v>
       </c>
       <c r="B139" t="s">
@@ -3055,8 +3660,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A140" s="9">
+    <row r="140" spans="1:5">
+      <c r="A140" s="8">
         <v>45350</v>
       </c>
       <c r="B140" t="s">
@@ -3072,8 +3677,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A141" s="9">
+    <row r="141" spans="1:5">
+      <c r="A141" s="8">
         <v>45351</v>
       </c>
       <c r="B141" t="s">
@@ -3089,8 +3694,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A142" s="9">
+    <row r="142" spans="1:5">
+      <c r="A142" s="8">
         <v>45352</v>
       </c>
       <c r="D142" t="s">
@@ -3100,8 +3705,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A143" s="9">
+    <row r="143" spans="1:5">
+      <c r="A143" s="8">
         <v>45353</v>
       </c>
       <c r="B143" t="s">
@@ -3117,8 +3722,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A144" s="9">
+    <row r="144" spans="1:5">
+      <c r="A144" s="8">
         <v>45354</v>
       </c>
       <c r="B144" t="s">
@@ -3127,44 +3732,65 @@
       <c r="C144" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A145" s="9">
+      <c r="D144" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="8">
         <v>45355</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A146" s="9">
+      <c r="D145" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="8">
         <v>45356</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A147" s="9">
+      <c r="D146" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="8">
         <v>45357</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A148" s="9">
+    <row r="148" spans="1:1">
+      <c r="A148" s="8">
         <v>45358</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A149" s="9">
+    <row r="149" spans="1:1">
+      <c r="A149" s="8">
         <v>45359</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F148" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter ref="A1:F149">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -3173,7 +3799,7 @@
     <col min="5" max="5" width="21.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>12</v>
       </c>
@@ -3190,7 +3816,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
         <v>17</v>
       </c>
@@ -3207,7 +3833,7 @@
         <v>45260</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -3221,10 +3847,10 @@
         <v>24</v>
       </c>
       <c r="E3" s="4">
-        <v>45318.423773148097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -3238,10 +3864,10 @@
         <v>24</v>
       </c>
       <c r="E4" s="4">
-        <v>45318.423773148097</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3255,10 +3881,10 @@
         <v>24</v>
       </c>
       <c r="E5" s="4">
-        <v>45318.423773148097</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3272,10 +3898,10 @@
         <v>24</v>
       </c>
       <c r="E6" s="4">
-        <v>45318.423773148097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+        <v>45318.4237731481</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3289,402 +3915,421 @@
         <v>34</v>
       </c>
       <c r="E7" s="4">
-        <v>45328.631655092599</v>
+        <v>45328.6316550926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="4">
+        <v>45356.5616550926</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E7" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter ref="A1:E7">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B28" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <autoFilter ref="A1:B28">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2">
         <v>100006</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3">
         <v>100033</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4">
         <v>100556</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5">
         <v>105470</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6">
         <v>153240</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7">
         <v>101398</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>